--- a/research/traditional_assets/database/data/kuwait/kuwait_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_packaging_container.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07832415348143706</v>
+        <v>0.07824491725121489</v>
       </c>
       <c r="C2">
-        <v>75.12743105310298</v>
+        <v>74.51793886731015</v>
       </c>
       <c r="D2">
-        <v>55.52743105310297</v>
+        <v>55.66303886731014</v>
       </c>
       <c r="E2">
-        <v>-6.21</v>
+        <v>-5.4649</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.7450999999999999</v>
       </c>
       <c r="G2">
         <v>19.6</v>
@@ -1451,28 +1451,28 @@
         <v>3.43</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.03747852999999999</v>
       </c>
       <c r="N2">
-        <v>3.43</v>
+        <v>3.39252147</v>
       </c>
       <c r="O2">
-        <v>0.5145</v>
+        <v>0.5088782205</v>
       </c>
       <c r="P2">
-        <v>2.9155</v>
+        <v>2.8836432495</v>
       </c>
       <c r="Q2">
-        <v>5.4255</v>
+        <v>5.3936432495</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07832415348143706</v>
+        <v>0.07860340126385343</v>
       </c>
       <c r="T2">
-        <v>0.6169711731246059</v>
+        <v>0.622268400368605</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>91.51906438166068</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07824491725121489</v>
+        <v>0.07816568102099275</v>
       </c>
       <c r="C3">
-        <v>74.51793886731015</v>
+        <v>73.90911065963526</v>
       </c>
       <c r="D3">
-        <v>55.66303886731014</v>
+        <v>55.79931065963527</v>
       </c>
       <c r="E3">
-        <v>-5.4649</v>
+        <v>-4.7198</v>
       </c>
       <c r="F3">
-        <v>0.7450999999999999</v>
+        <v>1.4902</v>
       </c>
       <c r="G3">
         <v>19.6</v>
@@ -1533,28 +1533,28 @@
         <v>3.43</v>
       </c>
       <c r="M3">
-        <v>0.03747852999999999</v>
+        <v>0.07495705999999998</v>
       </c>
       <c r="N3">
-        <v>3.39252147</v>
+        <v>3.35504294</v>
       </c>
       <c r="O3">
-        <v>0.5088782205</v>
+        <v>0.503256441</v>
       </c>
       <c r="P3">
-        <v>2.8836432495</v>
+        <v>2.851786499</v>
       </c>
       <c r="Q3">
-        <v>5.3936432495</v>
+        <v>5.361786499000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07860340126385343</v>
+        <v>0.07888834798060484</v>
       </c>
       <c r="T3">
-        <v>0.622268400368605</v>
+        <v>0.6276737342910532</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>91.51906438166068</v>
+        <v>45.75953219083034</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07816568102099275</v>
+        <v>0.07808644479077058</v>
       </c>
       <c r="C4">
-        <v>73.90911065963526</v>
+        <v>73.30095131861205</v>
       </c>
       <c r="D4">
-        <v>55.79931065963527</v>
+        <v>55.93625131861204</v>
       </c>
       <c r="E4">
-        <v>-4.7198</v>
+        <v>-3.9747</v>
       </c>
       <c r="F4">
-        <v>1.4902</v>
+        <v>2.2353</v>
       </c>
       <c r="G4">
         <v>19.6</v>
@@ -1615,28 +1615,28 @@
         <v>3.43</v>
       </c>
       <c r="M4">
-        <v>0.07495705999999998</v>
+        <v>0.11243559</v>
       </c>
       <c r="N4">
-        <v>3.35504294</v>
+        <v>3.31756441</v>
       </c>
       <c r="O4">
-        <v>0.503256441</v>
+        <v>0.4976346615</v>
       </c>
       <c r="P4">
-        <v>2.851786499</v>
+        <v>2.8199297485</v>
       </c>
       <c r="Q4">
-        <v>5.361786499000001</v>
+        <v>5.3299297485</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07888834798060484</v>
+        <v>0.07917916988739236</v>
       </c>
       <c r="T4">
-        <v>0.6276737342910532</v>
+        <v>0.6331905183974692</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>45.75953219083034</v>
+        <v>30.50635479388689</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07808644479077058</v>
+        <v>0.07800720856054844</v>
       </c>
       <c r="C5">
-        <v>73.30095131861205</v>
+        <v>72.69346578088103</v>
       </c>
       <c r="D5">
-        <v>55.93625131861204</v>
+        <v>56.07386578088103</v>
       </c>
       <c r="E5">
-        <v>-3.9747</v>
+        <v>-3.2296</v>
       </c>
       <c r="F5">
-        <v>2.2353</v>
+        <v>2.980399999999999</v>
       </c>
       <c r="G5">
         <v>19.6</v>
@@ -1697,28 +1697,28 @@
         <v>3.43</v>
       </c>
       <c r="M5">
-        <v>0.11243559</v>
+        <v>0.14991412</v>
       </c>
       <c r="N5">
-        <v>3.31756441</v>
+        <v>3.28008588</v>
       </c>
       <c r="O5">
-        <v>0.4976346615</v>
+        <v>0.492012882</v>
       </c>
       <c r="P5">
-        <v>2.8199297485</v>
+        <v>2.788072998</v>
       </c>
       <c r="Q5">
-        <v>5.3299297485</v>
+        <v>5.298072998</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07917916988739236</v>
+        <v>0.07947605058390463</v>
       </c>
       <c r="T5">
-        <v>0.6331905183974692</v>
+        <v>0.6388222355061024</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>30.50635479388689</v>
+        <v>22.87976609541517</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07800720856054844</v>
+        <v>0.07792797233032628</v>
       </c>
       <c r="C6">
-        <v>72.69346578088103</v>
+        <v>72.08665903178334</v>
       </c>
       <c r="D6">
-        <v>56.07386578088103</v>
+        <v>56.21215903178334</v>
       </c>
       <c r="E6">
-        <v>-3.2296</v>
+        <v>-2.4845</v>
       </c>
       <c r="F6">
-        <v>2.980399999999999</v>
+        <v>3.7255</v>
       </c>
       <c r="G6">
         <v>19.6</v>
@@ -1779,28 +1779,28 @@
         <v>3.43</v>
       </c>
       <c r="M6">
-        <v>0.14991412</v>
+        <v>0.18739265</v>
       </c>
       <c r="N6">
-        <v>3.28008588</v>
+        <v>3.24260735</v>
       </c>
       <c r="O6">
-        <v>0.492012882</v>
+        <v>0.4863911025</v>
       </c>
       <c r="P6">
-        <v>2.788072998</v>
+        <v>2.7562162475</v>
       </c>
       <c r="Q6">
-        <v>5.298072998</v>
+        <v>5.266216247500001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07947605058390463</v>
+        <v>0.07977918140034346</v>
       </c>
       <c r="T6">
-        <v>0.6388222355061024</v>
+        <v>0.6445725150801804</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>22.87976609541517</v>
+        <v>18.30381287633213</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07792797233032628</v>
+        <v>0.07784873610010412</v>
       </c>
       <c r="C7">
-        <v>72.08665903178334</v>
+        <v>71.48053610596232</v>
       </c>
       <c r="D7">
-        <v>56.21215903178334</v>
+        <v>56.35113610596232</v>
       </c>
       <c r="E7">
-        <v>-2.4845</v>
+        <v>-1.7394</v>
       </c>
       <c r="F7">
-        <v>3.7255</v>
+        <v>4.4706</v>
       </c>
       <c r="G7">
         <v>19.6</v>
@@ -1861,28 +1861,28 @@
         <v>3.43</v>
       </c>
       <c r="M7">
-        <v>0.18739265</v>
+        <v>0.22487118</v>
       </c>
       <c r="N7">
-        <v>3.24260735</v>
+        <v>3.20512882</v>
       </c>
       <c r="O7">
-        <v>0.4863911025</v>
+        <v>0.480769323</v>
       </c>
       <c r="P7">
-        <v>2.7562162475</v>
+        <v>2.724359497</v>
       </c>
       <c r="Q7">
-        <v>5.266216247500001</v>
+        <v>5.234359497</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07977918140034346</v>
+        <v>0.0800887618086214</v>
       </c>
       <c r="T7">
-        <v>0.6445725150801804</v>
+        <v>0.650445141028175</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>18.30381287633213</v>
+        <v>15.25317739694344</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07784873610010412</v>
+        <v>0.07776949986988198</v>
       </c>
       <c r="C8">
-        <v>71.48053610596232</v>
+        <v>70.87510208797471</v>
       </c>
       <c r="D8">
-        <v>56.35113610596232</v>
+        <v>56.4908020879747</v>
       </c>
       <c r="E8">
-        <v>-1.739400000000001</v>
+        <v>-0.9943000000000008</v>
       </c>
       <c r="F8">
-        <v>4.470599999999999</v>
+        <v>5.215699999999999</v>
       </c>
       <c r="G8">
         <v>19.6</v>
@@ -1943,28 +1943,28 @@
         <v>3.43</v>
       </c>
       <c r="M8">
-        <v>0.2248711799999999</v>
+        <v>0.26234971</v>
       </c>
       <c r="N8">
-        <v>3.20512882</v>
+        <v>3.16765029</v>
       </c>
       <c r="O8">
-        <v>0.480769323</v>
+        <v>0.4751475435</v>
       </c>
       <c r="P8">
-        <v>2.724359497</v>
+        <v>2.6925027465</v>
       </c>
       <c r="Q8">
-        <v>5.234359497</v>
+        <v>5.2025027465</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0800887618086214</v>
+        <v>0.08040499986008814</v>
       </c>
       <c r="T8">
-        <v>0.650445141028175</v>
+        <v>0.6564440600073091</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.25317739694344</v>
+        <v>13.07415205452295</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07776949986988198</v>
+        <v>0.07779226363965981</v>
       </c>
       <c r="C9">
-        <v>70.87510208797471</v>
+        <v>70.08980663235516</v>
       </c>
       <c r="D9">
-        <v>56.4908020879747</v>
+        <v>56.45060663235517</v>
       </c>
       <c r="E9">
-        <v>-0.9943</v>
+        <v>-0.249200000000001</v>
       </c>
       <c r="F9">
-        <v>5.2157</v>
+        <v>5.960799999999999</v>
       </c>
       <c r="G9">
         <v>19.6</v>
@@ -2025,45 +2025,45 @@
         <v>3.43</v>
       </c>
       <c r="M9">
-        <v>0.26234971</v>
+        <v>0.30876944</v>
       </c>
       <c r="N9">
-        <v>3.16765029</v>
+        <v>3.12123056</v>
       </c>
       <c r="O9">
-        <v>0.4751475435</v>
+        <v>0.468184584</v>
       </c>
       <c r="P9">
-        <v>2.6925027465</v>
+        <v>2.653045976</v>
       </c>
       <c r="Q9">
-        <v>5.2025027465</v>
+        <v>5.163045976000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08040499986008814</v>
+        <v>0.08072811265180414</v>
       </c>
       <c r="T9">
-        <v>0.6564440600073091</v>
+        <v>0.6625733902685985</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.15</v>
       </c>
       <c r="W9">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.07415205452295</v>
+        <v>11.10861230308285</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07779226363965981</v>
+        <v>0.07772577740943766</v>
       </c>
       <c r="C10">
-        <v>70.08980663235516</v>
+        <v>69.46226643303304</v>
       </c>
       <c r="D10">
-        <v>56.45060663235517</v>
+        <v>56.56816643303303</v>
       </c>
       <c r="E10">
-        <v>-0.249200000000001</v>
+        <v>0.4958999999999989</v>
       </c>
       <c r="F10">
-        <v>5.960799999999999</v>
+        <v>6.705899999999999</v>
       </c>
       <c r="G10">
         <v>19.6</v>
@@ -2107,28 +2107,28 @@
         <v>3.43</v>
       </c>
       <c r="M10">
-        <v>0.30876944</v>
+        <v>0.3473656199999999</v>
       </c>
       <c r="N10">
-        <v>3.12123056</v>
+        <v>3.08263438</v>
       </c>
       <c r="O10">
-        <v>0.468184584</v>
+        <v>0.462395157</v>
       </c>
       <c r="P10">
-        <v>2.653045976</v>
+        <v>2.620239223</v>
       </c>
       <c r="Q10">
-        <v>5.163045976000001</v>
+        <v>5.130239223</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08072811265180414</v>
+        <v>0.08105832682355786</v>
       </c>
       <c r="T10">
-        <v>0.6625733902685985</v>
+        <v>0.668837431085081</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.10861230308285</v>
+        <v>9.874322047184751</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07772577740943766</v>
+        <v>0.07780379117921551</v>
       </c>
       <c r="C11">
-        <v>69.46226643303304</v>
+        <v>68.57927352252911</v>
       </c>
       <c r="D11">
-        <v>56.56816643303303</v>
+        <v>56.4302735225291</v>
       </c>
       <c r="E11">
-        <v>0.4958999999999989</v>
+        <v>1.240999999999999</v>
       </c>
       <c r="F11">
-        <v>6.705899999999999</v>
+        <v>7.450999999999999</v>
       </c>
       <c r="G11">
         <v>19.6</v>
@@ -2189,45 +2189,45 @@
         <v>3.43</v>
       </c>
       <c r="M11">
-        <v>0.3473656199999999</v>
+        <v>0.3986284999999999</v>
       </c>
       <c r="N11">
-        <v>3.08263438</v>
+        <v>3.0313715</v>
       </c>
       <c r="O11">
-        <v>0.462395157</v>
+        <v>0.454705725</v>
       </c>
       <c r="P11">
-        <v>2.620239223</v>
+        <v>2.576665775</v>
       </c>
       <c r="Q11">
-        <v>5.130239223</v>
+        <v>5.086665775</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08105832682355786</v>
+        <v>0.08139587908801724</v>
       </c>
       <c r="T11">
-        <v>0.668837431085081</v>
+        <v>0.6752406728085966</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.15</v>
       </c>
       <c r="W11">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>9.874322047184751</v>
+        <v>8.604502688593517</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07780379117921551</v>
+        <v>0.07775175494899335</v>
       </c>
       <c r="C12">
-        <v>68.57927352252911</v>
+        <v>67.92607516327483</v>
       </c>
       <c r="D12">
-        <v>56.4302735225291</v>
+        <v>56.52217516327483</v>
       </c>
       <c r="E12">
-        <v>1.241</v>
+        <v>1.9861</v>
       </c>
       <c r="F12">
-        <v>7.451</v>
+        <v>8.196099999999999</v>
       </c>
       <c r="G12">
         <v>19.6</v>
@@ -2271,28 +2271,28 @@
         <v>3.43</v>
       </c>
       <c r="M12">
-        <v>0.3986285</v>
+        <v>0.4384913499999999</v>
       </c>
       <c r="N12">
-        <v>3.0313715</v>
+        <v>2.99150865</v>
       </c>
       <c r="O12">
-        <v>0.454705725</v>
+        <v>0.4487262975</v>
       </c>
       <c r="P12">
-        <v>2.576665775</v>
+        <v>2.5427823525</v>
       </c>
       <c r="Q12">
-        <v>5.086665775</v>
+        <v>5.0527823525</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08139587908801724</v>
+        <v>0.08174101679662174</v>
       </c>
       <c r="T12">
-        <v>0.6752406728085966</v>
+        <v>0.6817878076045505</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.604502688593517</v>
+        <v>7.822275171448651</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07775175494899335</v>
+        <v>0.0777813187187712</v>
       </c>
       <c r="C13">
-        <v>67.92607516327483</v>
+        <v>67.1287256425917</v>
       </c>
       <c r="D13">
-        <v>56.52217516327483</v>
+        <v>56.4699256425917</v>
       </c>
       <c r="E13">
-        <v>1.9861</v>
+        <v>2.731199999999999</v>
       </c>
       <c r="F13">
-        <v>8.196099999999999</v>
+        <v>8.941199999999998</v>
       </c>
       <c r="G13">
         <v>19.6</v>
@@ -2353,45 +2353,45 @@
         <v>3.43</v>
       </c>
       <c r="M13">
-        <v>0.4384913499999999</v>
+        <v>0.4855071599999999</v>
       </c>
       <c r="N13">
-        <v>2.99150865</v>
+        <v>2.94449284</v>
       </c>
       <c r="O13">
-        <v>0.4487262975</v>
+        <v>0.441673926</v>
       </c>
       <c r="P13">
-        <v>2.5427823525</v>
+        <v>2.502818914</v>
       </c>
       <c r="Q13">
-        <v>5.0527823525</v>
+        <v>5.012818914</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08174101679662174</v>
+        <v>0.08209399854405817</v>
       </c>
       <c r="T13">
-        <v>0.6817878076045505</v>
+        <v>0.6884837409185943</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.15</v>
       </c>
       <c r="W13">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>7.822275171448651</v>
+        <v>7.064777376300692</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0777813187187712</v>
+        <v>0.07773608248854903</v>
       </c>
       <c r="C14">
-        <v>67.1287256425917</v>
+        <v>66.4636131162561</v>
       </c>
       <c r="D14">
-        <v>56.4699256425917</v>
+        <v>56.54991311625609</v>
       </c>
       <c r="E14">
-        <v>2.731199999999999</v>
+        <v>3.476299999999999</v>
       </c>
       <c r="F14">
-        <v>8.941199999999998</v>
+        <v>9.686299999999999</v>
       </c>
       <c r="G14">
         <v>19.6</v>
@@ -2435,28 +2435,28 @@
         <v>3.43</v>
       </c>
       <c r="M14">
-        <v>0.4855071599999999</v>
+        <v>0.5259660899999999</v>
       </c>
       <c r="N14">
-        <v>2.94449284</v>
+        <v>2.90403391</v>
       </c>
       <c r="O14">
-        <v>0.441673926</v>
+        <v>0.4356050865</v>
       </c>
       <c r="P14">
-        <v>2.502818914</v>
+        <v>2.4684288235</v>
       </c>
       <c r="Q14">
-        <v>5.012818914</v>
+        <v>4.978428823500001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08209399854405817</v>
+        <v>0.08245509481442417</v>
       </c>
       <c r="T14">
-        <v>0.6884837409185943</v>
+        <v>0.6953336037341105</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.064777376300692</v>
+        <v>6.521332962739101</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07773608248854903</v>
+        <v>0.07780984625832686</v>
       </c>
       <c r="C15">
-        <v>66.4636131162561</v>
+        <v>65.58819900170522</v>
       </c>
       <c r="D15">
-        <v>56.54991311625609</v>
+        <v>56.41959900170522</v>
       </c>
       <c r="E15">
-        <v>3.476299999999999</v>
+        <v>4.2214</v>
       </c>
       <c r="F15">
-        <v>9.686299999999999</v>
+        <v>10.4314</v>
       </c>
       <c r="G15">
         <v>19.6</v>
@@ -2517,45 +2517,45 @@
         <v>3.43</v>
       </c>
       <c r="M15">
-        <v>0.5259660899999999</v>
+        <v>0.57685642</v>
       </c>
       <c r="N15">
-        <v>2.90403391</v>
+        <v>2.85314358</v>
       </c>
       <c r="O15">
-        <v>0.4356050865</v>
+        <v>0.427971537</v>
       </c>
       <c r="P15">
-        <v>2.4684288235</v>
+        <v>2.425172043</v>
       </c>
       <c r="Q15">
-        <v>4.978428823500001</v>
+        <v>4.935172043000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08245509481442417</v>
+        <v>0.08282458867247311</v>
       </c>
       <c r="T15">
-        <v>0.6953336037341105</v>
+        <v>0.7023427656848711</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.15</v>
       </c>
       <c r="W15">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>6.521332962739101</v>
+        <v>5.946020328594072</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07780984625832686</v>
+        <v>0.07777311002810472</v>
       </c>
       <c r="C16">
-        <v>65.58819900170522</v>
+        <v>64.90792358011331</v>
       </c>
       <c r="D16">
-        <v>56.41959900170522</v>
+        <v>56.48442358011331</v>
       </c>
       <c r="E16">
-        <v>4.2214</v>
+        <v>4.966500000000001</v>
       </c>
       <c r="F16">
-        <v>10.4314</v>
+        <v>11.1765</v>
       </c>
       <c r="G16">
         <v>19.6</v>
@@ -2599,28 +2599,28 @@
         <v>3.43</v>
       </c>
       <c r="M16">
-        <v>0.57685642</v>
+        <v>0.6180604500000001</v>
       </c>
       <c r="N16">
-        <v>2.85314358</v>
+        <v>2.81193955</v>
       </c>
       <c r="O16">
-        <v>0.427971537</v>
+        <v>0.4217909325</v>
       </c>
       <c r="P16">
-        <v>2.425172043</v>
+        <v>2.3901486175</v>
       </c>
       <c r="Q16">
-        <v>4.935172043000001</v>
+        <v>4.9001486175</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08282458867247311</v>
+        <v>0.08320277650365261</v>
       </c>
       <c r="T16">
-        <v>0.7023427656848711</v>
+        <v>0.7095168490932967</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.946020328594072</v>
+        <v>5.549618973354466</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07777311002810472</v>
+        <v>0.07773637379788256</v>
       </c>
       <c r="C17">
-        <v>64.90792358011331</v>
+        <v>64.22779729321353</v>
       </c>
       <c r="D17">
-        <v>56.48442358011331</v>
+        <v>56.54939729321353</v>
       </c>
       <c r="E17">
-        <v>4.966499999999999</v>
+        <v>5.711599999999998</v>
       </c>
       <c r="F17">
-        <v>11.1765</v>
+        <v>11.9216</v>
       </c>
       <c r="G17">
         <v>19.6</v>
@@ -2681,28 +2681,28 @@
         <v>3.43</v>
       </c>
       <c r="M17">
-        <v>0.61806045</v>
+        <v>0.6592644799999999</v>
       </c>
       <c r="N17">
-        <v>2.81193955</v>
+        <v>2.77073552</v>
       </c>
       <c r="O17">
-        <v>0.4217909325</v>
+        <v>0.415610328</v>
       </c>
       <c r="P17">
-        <v>2.3901486175</v>
+        <v>2.355125192</v>
       </c>
       <c r="Q17">
-        <v>4.9001486175</v>
+        <v>4.865125192000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08320277650365261</v>
+        <v>0.08358996880700306</v>
       </c>
       <c r="T17">
-        <v>0.7095168490932967</v>
+        <v>0.716861744011447</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.549618973354467</v>
+        <v>5.202767787519814</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07773637379788256</v>
+        <v>0.07769963756766041</v>
       </c>
       <c r="C18">
-        <v>64.22779729321353</v>
+        <v>63.5478206562449</v>
       </c>
       <c r="D18">
-        <v>56.54939729321353</v>
+        <v>56.61452065624489</v>
       </c>
       <c r="E18">
-        <v>5.711599999999998</v>
+        <v>6.456699999999999</v>
       </c>
       <c r="F18">
-        <v>11.9216</v>
+        <v>12.6667</v>
       </c>
       <c r="G18">
         <v>19.6</v>
@@ -2763,28 +2763,28 @@
         <v>3.43</v>
       </c>
       <c r="M18">
-        <v>0.6592644799999999</v>
+        <v>0.70046851</v>
       </c>
       <c r="N18">
-        <v>2.77073552</v>
+        <v>2.72953149</v>
       </c>
       <c r="O18">
-        <v>0.415610328</v>
+        <v>0.4094297235</v>
       </c>
       <c r="P18">
-        <v>2.355125192</v>
+        <v>2.3201017665</v>
       </c>
       <c r="Q18">
-        <v>4.865125192000001</v>
+        <v>4.8301017665</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08358996880700306</v>
+        <v>0.08398649104537399</v>
       </c>
       <c r="T18">
-        <v>0.716861744011447</v>
+        <v>0.7243836243493114</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.202767787519814</v>
+        <v>4.89672262354806</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07769963756766041</v>
+        <v>0.07766290133743825</v>
       </c>
       <c r="C19">
-        <v>63.5478206562449</v>
+        <v>62.86799418682264</v>
       </c>
       <c r="D19">
-        <v>56.61452065624489</v>
+        <v>56.67979418682263</v>
       </c>
       <c r="E19">
-        <v>6.456699999999999</v>
+        <v>7.2018</v>
       </c>
       <c r="F19">
-        <v>12.6667</v>
+        <v>13.4118</v>
       </c>
       <c r="G19">
         <v>19.6</v>
@@ -2845,28 +2845,28 @@
         <v>3.43</v>
       </c>
       <c r="M19">
-        <v>0.70046851</v>
+        <v>0.74167254</v>
       </c>
       <c r="N19">
-        <v>2.72953149</v>
+        <v>2.68832746</v>
       </c>
       <c r="O19">
-        <v>0.4094297235</v>
+        <v>0.403249119</v>
       </c>
       <c r="P19">
-        <v>2.3201017665</v>
+        <v>2.285078341</v>
       </c>
       <c r="Q19">
-        <v>4.8301017665</v>
+        <v>4.795078341</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08398649104537399</v>
+        <v>0.08439268455785154</v>
       </c>
       <c r="T19">
-        <v>0.7243836243493114</v>
+        <v>0.7320889651832214</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.89672262354806</v>
+        <v>4.624682477795389</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07766290133743826</v>
+        <v>0.0780299151072161</v>
       </c>
       <c r="C20">
-        <v>62.8679941868226</v>
+        <v>61.47746074818225</v>
       </c>
       <c r="D20">
-        <v>56.6797941868226</v>
+        <v>56.03436074818224</v>
       </c>
       <c r="E20">
-        <v>7.201799999999998</v>
+        <v>7.946899999999999</v>
       </c>
       <c r="F20">
-        <v>13.4118</v>
+        <v>14.1569</v>
       </c>
       <c r="G20">
         <v>19.6</v>
@@ -2927,45 +2927,45 @@
         <v>3.43</v>
       </c>
       <c r="M20">
-        <v>0.7416725399999999</v>
+        <v>0.81826882</v>
       </c>
       <c r="N20">
-        <v>2.68832746</v>
+        <v>2.61173118</v>
       </c>
       <c r="O20">
-        <v>0.403249119</v>
+        <v>0.391759677</v>
       </c>
       <c r="P20">
-        <v>2.285078341</v>
+        <v>2.219971503</v>
       </c>
       <c r="Q20">
-        <v>4.795078341</v>
+        <v>4.729971503</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08439268455785154</v>
+        <v>0.08480890753977297</v>
       </c>
       <c r="T20">
-        <v>0.7320889651832214</v>
+        <v>0.7399845613463637</v>
       </c>
       <c r="U20">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V20">
         <v>0.15</v>
       </c>
       <c r="W20">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.624682477795389</v>
+        <v>4.191776487340676</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0780299151072161</v>
+        <v>0.07860942887699394</v>
       </c>
       <c r="C21">
-        <v>61.47746074818225</v>
+        <v>59.74262442098147</v>
       </c>
       <c r="D21">
-        <v>56.03436074818224</v>
+        <v>55.04462442098146</v>
       </c>
       <c r="E21">
-        <v>7.946899999999999</v>
+        <v>8.692</v>
       </c>
       <c r="F21">
-        <v>14.1569</v>
+        <v>14.902</v>
       </c>
       <c r="G21">
         <v>19.6</v>
@@ -3009,45 +3009,45 @@
         <v>3.43</v>
       </c>
       <c r="M21">
-        <v>0.81826882</v>
+        <v>0.9134926</v>
       </c>
       <c r="N21">
-        <v>2.61173118</v>
+        <v>2.5165074</v>
       </c>
       <c r="O21">
-        <v>0.391759677</v>
+        <v>0.37747611</v>
       </c>
       <c r="P21">
-        <v>2.219971503</v>
+        <v>2.13903129</v>
       </c>
       <c r="Q21">
-        <v>4.729971503</v>
+        <v>4.64903129</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08480890753977297</v>
+        <v>0.08523553609624243</v>
       </c>
       <c r="T21">
-        <v>0.7399845613463637</v>
+        <v>0.7480775474135847</v>
       </c>
       <c r="U21">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.191776487340676</v>
+        <v>3.754819688741868</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07860942887699394</v>
+        <v>0.07862369264677178</v>
       </c>
       <c r="C22">
-        <v>59.74262442098147</v>
+        <v>58.97360438679464</v>
       </c>
       <c r="D22">
-        <v>55.04462442098146</v>
+        <v>55.02070438679464</v>
       </c>
       <c r="E22">
-        <v>8.692</v>
+        <v>9.437100000000001</v>
       </c>
       <c r="F22">
-        <v>14.902</v>
+        <v>15.6471</v>
       </c>
       <c r="G22">
         <v>19.6</v>
@@ -3091,28 +3091,28 @@
         <v>3.43</v>
       </c>
       <c r="M22">
-        <v>0.9134926</v>
+        <v>0.95916723</v>
       </c>
       <c r="N22">
-        <v>2.5165074</v>
+        <v>2.47083277</v>
       </c>
       <c r="O22">
-        <v>0.37747611</v>
+        <v>0.3706249155</v>
       </c>
       <c r="P22">
-        <v>2.13903129</v>
+        <v>2.1002078545</v>
       </c>
       <c r="Q22">
-        <v>4.64903129</v>
+        <v>4.6102078545</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08523553609624243</v>
+        <v>0.08567296537566049</v>
       </c>
       <c r="T22">
-        <v>0.7480775474135847</v>
+        <v>0.7563754192040264</v>
       </c>
       <c r="U22">
         <v>0.0613</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.754819688741868</v>
+        <v>3.576018751182732</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07862369264677178</v>
+        <v>0.07916155641654964</v>
       </c>
       <c r="C23">
-        <v>58.97360438679465</v>
+        <v>57.34144614802993</v>
       </c>
       <c r="D23">
-        <v>55.02070438679464</v>
+        <v>54.13364614802993</v>
       </c>
       <c r="E23">
-        <v>9.437099999999997</v>
+        <v>10.1822</v>
       </c>
       <c r="F23">
-        <v>15.6471</v>
+        <v>16.3922</v>
       </c>
       <c r="G23">
         <v>19.6</v>
@@ -3173,45 +3173,45 @@
         <v>3.43</v>
       </c>
       <c r="M23">
-        <v>0.9591672299999999</v>
+        <v>1.05074002</v>
       </c>
       <c r="N23">
-        <v>2.47083277</v>
+        <v>2.37925998</v>
       </c>
       <c r="O23">
-        <v>0.3706249155</v>
+        <v>0.356888997</v>
       </c>
       <c r="P23">
-        <v>2.1002078545</v>
+        <v>2.022370983</v>
       </c>
       <c r="Q23">
-        <v>4.6102078545</v>
+        <v>4.532370983</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08567296537566049</v>
+        <v>0.08612161079044825</v>
       </c>
       <c r="T23">
-        <v>0.7563754192040263</v>
+        <v>0.7648860569378128</v>
       </c>
       <c r="U23">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V23">
         <v>0.15</v>
       </c>
       <c r="W23">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.576018751182732</v>
+        <v>3.264366003685669</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07916155641654964</v>
+        <v>0.07919962018632749</v>
       </c>
       <c r="C24">
-        <v>57.34144614802993</v>
+        <v>56.5346529122171</v>
       </c>
       <c r="D24">
-        <v>54.13364614802993</v>
+        <v>54.07195291221709</v>
       </c>
       <c r="E24">
-        <v>10.1822</v>
+        <v>10.9273</v>
       </c>
       <c r="F24">
-        <v>16.3922</v>
+        <v>17.1373</v>
       </c>
       <c r="G24">
         <v>19.6</v>
@@ -3255,28 +3255,28 @@
         <v>3.43</v>
       </c>
       <c r="M24">
-        <v>1.05074002</v>
+        <v>1.09850093</v>
       </c>
       <c r="N24">
-        <v>2.37925998</v>
+        <v>2.33149907</v>
       </c>
       <c r="O24">
-        <v>0.356888997</v>
+        <v>0.3497248605</v>
       </c>
       <c r="P24">
-        <v>2.022370983</v>
+        <v>1.9817742095</v>
       </c>
       <c r="Q24">
-        <v>4.532370983</v>
+        <v>4.4917742095</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08612161079044825</v>
+        <v>0.08658190933289284</v>
       </c>
       <c r="T24">
-        <v>0.7648860569378128</v>
+        <v>0.773617750197152</v>
       </c>
       <c r="U24">
         <v>0.0641</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.264366003685669</v>
+        <v>3.122437047003683</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07919962018632749</v>
+        <v>0.08082888395610532</v>
       </c>
       <c r="C25">
-        <v>56.5346529122171</v>
+        <v>53.27455774561678</v>
       </c>
       <c r="D25">
-        <v>54.07195291221709</v>
+        <v>51.55695774561678</v>
       </c>
       <c r="E25">
-        <v>10.9273</v>
+        <v>11.6724</v>
       </c>
       <c r="F25">
-        <v>17.1373</v>
+        <v>17.8824</v>
       </c>
       <c r="G25">
         <v>19.6</v>
@@ -3337,45 +3337,45 @@
         <v>3.43</v>
       </c>
       <c r="M25">
-        <v>1.09850093</v>
+        <v>1.28574456</v>
       </c>
       <c r="N25">
-        <v>2.33149907</v>
+        <v>2.14425544</v>
       </c>
       <c r="O25">
-        <v>0.3497248605</v>
+        <v>0.321638316</v>
       </c>
       <c r="P25">
-        <v>1.9817742095</v>
+        <v>1.822617124</v>
       </c>
       <c r="Q25">
-        <v>4.4917742095</v>
+        <v>4.332617124</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08658190933289284</v>
+        <v>0.08705432099487542</v>
       </c>
       <c r="T25">
-        <v>0.773617750197152</v>
+        <v>0.7825792248580528</v>
       </c>
       <c r="U25">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V25">
         <v>0.15</v>
       </c>
       <c r="W25">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.122437047003683</v>
+        <v>2.667714961982806</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08082888395610532</v>
+        <v>0.08093324772588317</v>
       </c>
       <c r="C26">
-        <v>53.27455774561678</v>
+        <v>52.37630713140112</v>
       </c>
       <c r="D26">
-        <v>51.55695774561678</v>
+        <v>51.40380713140112</v>
       </c>
       <c r="E26">
-        <v>11.6724</v>
+        <v>12.4175</v>
       </c>
       <c r="F26">
-        <v>17.8824</v>
+        <v>18.6275</v>
       </c>
       <c r="G26">
         <v>19.6</v>
@@ -3419,28 +3419,28 @@
         <v>3.43</v>
       </c>
       <c r="M26">
-        <v>1.28574456</v>
+        <v>1.33931725</v>
       </c>
       <c r="N26">
-        <v>2.14425544</v>
+        <v>2.09068275</v>
       </c>
       <c r="O26">
-        <v>0.321638316</v>
+        <v>0.3136024125</v>
       </c>
       <c r="P26">
-        <v>1.822617124</v>
+        <v>1.7770803375</v>
       </c>
       <c r="Q26">
-        <v>4.332617124</v>
+        <v>4.287080337500001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08705432099487542</v>
+        <v>0.08753933030117755</v>
       </c>
       <c r="T26">
-        <v>0.7825792248580528</v>
+        <v>0.7917796721765775</v>
       </c>
       <c r="U26">
         <v>0.07190000000000001</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.667714961982806</v>
+        <v>2.561006363503494</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08093324772588317</v>
+        <v>0.08189951149566101</v>
       </c>
       <c r="C27">
-        <v>52.37630713140112</v>
+        <v>50.25529830599526</v>
       </c>
       <c r="D27">
-        <v>51.40380713140112</v>
+        <v>50.02789830599526</v>
       </c>
       <c r="E27">
-        <v>12.4175</v>
+        <v>13.1626</v>
       </c>
       <c r="F27">
-        <v>18.6275</v>
+        <v>19.3726</v>
       </c>
       <c r="G27">
         <v>19.6</v>
@@ -3501,45 +3501,45 @@
         <v>3.43</v>
       </c>
       <c r="M27">
-        <v>1.33931725</v>
+        <v>1.46844308</v>
       </c>
       <c r="N27">
-        <v>2.09068275</v>
+        <v>1.96155692</v>
       </c>
       <c r="O27">
-        <v>0.3136024125</v>
+        <v>0.294233538</v>
       </c>
       <c r="P27">
-        <v>1.7770803375</v>
+        <v>1.667323382</v>
       </c>
       <c r="Q27">
-        <v>4.287080337500001</v>
+        <v>4.177323382000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08753933030117755</v>
+        <v>0.08803744796710947</v>
       </c>
       <c r="T27">
-        <v>0.7917796721765775</v>
+        <v>0.8012287802334409</v>
       </c>
       <c r="U27">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V27">
         <v>0.15</v>
       </c>
       <c r="W27">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.561006363503494</v>
+        <v>2.335807255123569</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08189951149566101</v>
+        <v>0.08203702526543885</v>
       </c>
       <c r="C28">
-        <v>50.25529830599526</v>
+        <v>49.32035035794415</v>
       </c>
       <c r="D28">
-        <v>50.02789830599526</v>
+        <v>49.83805035794414</v>
       </c>
       <c r="E28">
-        <v>13.1626</v>
+        <v>13.9077</v>
       </c>
       <c r="F28">
-        <v>19.3726</v>
+        <v>20.1177</v>
       </c>
       <c r="G28">
         <v>19.6</v>
@@ -3583,28 +3583,28 @@
         <v>3.43</v>
       </c>
       <c r="M28">
-        <v>1.46844308</v>
+        <v>1.52492166</v>
       </c>
       <c r="N28">
-        <v>1.96155692</v>
+        <v>1.90507834</v>
       </c>
       <c r="O28">
-        <v>0.294233538</v>
+        <v>0.285761751</v>
       </c>
       <c r="P28">
-        <v>1.667323382</v>
+        <v>1.619316589</v>
       </c>
       <c r="Q28">
-        <v>4.177323382000001</v>
+        <v>4.129316589</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08803744796710947</v>
+        <v>0.088549212692382</v>
       </c>
       <c r="T28">
-        <v>0.8012287802334409</v>
+        <v>0.8109367679630951</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.335807255123569</v>
+        <v>2.249295875304178</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08203702526543885</v>
+        <v>0.08217453903521671</v>
       </c>
       <c r="C29">
-        <v>49.32035035794415</v>
+        <v>48.38683784840101</v>
       </c>
       <c r="D29">
-        <v>49.83805035794414</v>
+        <v>49.64963784840101</v>
       </c>
       <c r="E29">
-        <v>13.9077</v>
+        <v>14.6528</v>
       </c>
       <c r="F29">
-        <v>20.1177</v>
+        <v>20.8628</v>
       </c>
       <c r="G29">
         <v>19.6</v>
@@ -3665,28 +3665,28 @@
         <v>3.43</v>
       </c>
       <c r="M29">
-        <v>1.52492166</v>
+        <v>1.58140024</v>
       </c>
       <c r="N29">
-        <v>1.90507834</v>
+        <v>1.84859976</v>
       </c>
       <c r="O29">
-        <v>0.285761751</v>
+        <v>0.277289964</v>
       </c>
       <c r="P29">
-        <v>1.619316589</v>
+        <v>1.571309796</v>
       </c>
       <c r="Q29">
-        <v>4.129316589</v>
+        <v>4.081309796</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.088549212692382</v>
+        <v>0.08907519310446765</v>
       </c>
       <c r="T29">
-        <v>0.8109367679630951</v>
+        <v>0.820914422018573</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.249295875304178</v>
+        <v>2.1689638797576</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08217453903521671</v>
+        <v>0.08231205280499454</v>
       </c>
       <c r="C30">
-        <v>48.38683784840101</v>
+        <v>47.4547445586755</v>
       </c>
       <c r="D30">
-        <v>49.64963784840101</v>
+        <v>49.4626445586755</v>
       </c>
       <c r="E30">
-        <v>14.6528</v>
+        <v>15.3979</v>
       </c>
       <c r="F30">
-        <v>20.8628</v>
+        <v>21.6079</v>
       </c>
       <c r="G30">
         <v>19.6</v>
@@ -3747,28 +3747,28 @@
         <v>3.43</v>
       </c>
       <c r="M30">
-        <v>1.58140024</v>
+        <v>1.63787882</v>
       </c>
       <c r="N30">
-        <v>1.84859976</v>
+        <v>1.79212118</v>
       </c>
       <c r="O30">
-        <v>0.277289964</v>
+        <v>0.268818177</v>
       </c>
       <c r="P30">
-        <v>1.571309796</v>
+        <v>1.523303003</v>
       </c>
       <c r="Q30">
-        <v>4.081309796</v>
+        <v>4.033303003</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08907519310446765</v>
+        <v>0.0896159898661895</v>
       </c>
       <c r="T30">
-        <v>0.820914422018573</v>
+        <v>0.8311731367516698</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.1689638797576</v>
+        <v>2.094172021834924</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08231205280499454</v>
+        <v>0.0824495665747724</v>
       </c>
       <c r="C31">
-        <v>47.4547445586755</v>
+        <v>46.52405451349533</v>
       </c>
       <c r="D31">
-        <v>49.4626445586755</v>
+        <v>49.27705451349532</v>
       </c>
       <c r="E31">
-        <v>15.3979</v>
+        <v>16.143</v>
       </c>
       <c r="F31">
-        <v>21.6079</v>
+        <v>22.353</v>
       </c>
       <c r="G31">
         <v>19.6</v>
@@ -3829,28 +3829,28 @@
         <v>3.43</v>
       </c>
       <c r="M31">
-        <v>1.63787882</v>
+        <v>1.6943574</v>
       </c>
       <c r="N31">
-        <v>1.79212118</v>
+        <v>1.7356426</v>
       </c>
       <c r="O31">
-        <v>0.268818177</v>
+        <v>0.26034639</v>
       </c>
       <c r="P31">
-        <v>1.523303003</v>
+        <v>1.47529621</v>
       </c>
       <c r="Q31">
-        <v>4.033303003</v>
+        <v>3.98529621</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0896159898661895</v>
+        <v>0.09017223796396057</v>
       </c>
       <c r="T31">
-        <v>0.8311731367516698</v>
+        <v>0.8417249576199981</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.094172021834924</v>
+        <v>2.02436628777376</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0824495665747724</v>
+        <v>0.08632878034455024</v>
       </c>
       <c r="C32">
-        <v>46.52405451349533</v>
+        <v>41.06239934510006</v>
       </c>
       <c r="D32">
-        <v>49.27705451349532</v>
+        <v>44.56049934510006</v>
       </c>
       <c r="E32">
-        <v>16.143</v>
+        <v>16.8881</v>
       </c>
       <c r="F32">
-        <v>22.353</v>
+        <v>23.0981</v>
       </c>
       <c r="G32">
         <v>19.6</v>
@@ -3911,45 +3911,45 @@
         <v>3.43</v>
       </c>
       <c r="M32">
-        <v>1.6943574</v>
+        <v>2.078829</v>
       </c>
       <c r="N32">
-        <v>1.7356426</v>
+        <v>1.351171</v>
       </c>
       <c r="O32">
-        <v>0.26034639</v>
+        <v>0.20267565</v>
       </c>
       <c r="P32">
-        <v>1.47529621</v>
+        <v>1.14849535</v>
       </c>
       <c r="Q32">
-        <v>3.98529621</v>
+        <v>3.658495350000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09017223796396057</v>
+        <v>0.09074460919500035</v>
       </c>
       <c r="T32">
-        <v>0.8417249576199981</v>
+        <v>0.8525826283685678</v>
       </c>
       <c r="U32">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V32">
         <v>0.15</v>
       </c>
       <c r="W32">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.02436628777376</v>
+        <v>1.649967361432807</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08632878034455024</v>
+        <v>0.08658699411432808</v>
       </c>
       <c r="C33">
-        <v>41.06239934510006</v>
+        <v>40.03519631767842</v>
       </c>
       <c r="D33">
-        <v>44.56049934510006</v>
+        <v>44.27839631767841</v>
       </c>
       <c r="E33">
-        <v>16.8881</v>
+        <v>17.6332</v>
       </c>
       <c r="F33">
-        <v>23.0981</v>
+        <v>23.8432</v>
       </c>
       <c r="G33">
         <v>19.6</v>
@@ -3993,28 +3993,28 @@
         <v>3.43</v>
       </c>
       <c r="M33">
-        <v>2.078829</v>
+        <v>2.145887999999999</v>
       </c>
       <c r="N33">
-        <v>1.351171</v>
+        <v>1.284112000000001</v>
       </c>
       <c r="O33">
-        <v>0.20267565</v>
+        <v>0.1926168000000001</v>
       </c>
       <c r="P33">
-        <v>1.14849535</v>
+        <v>1.091495200000001</v>
       </c>
       <c r="Q33">
-        <v>3.658495350000001</v>
+        <v>3.601495200000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09074460919500035</v>
+        <v>0.09133381487401188</v>
       </c>
       <c r="T33">
-        <v>0.8525826283685678</v>
+        <v>0.8637596423744482</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.649967361432807</v>
+        <v>1.598405881388032</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08658699411432808</v>
+        <v>0.08684520788410592</v>
       </c>
       <c r="C34">
-        <v>40.03519631767842</v>
+        <v>39.01154268810032</v>
       </c>
       <c r="D34">
-        <v>44.27839631767841</v>
+        <v>43.99984268810032</v>
       </c>
       <c r="E34">
-        <v>17.6332</v>
+        <v>18.3783</v>
       </c>
       <c r="F34">
-        <v>23.8432</v>
+        <v>24.5883</v>
       </c>
       <c r="G34">
         <v>19.6</v>
@@ -4075,28 +4075,28 @@
         <v>3.43</v>
       </c>
       <c r="M34">
-        <v>2.145887999999999</v>
+        <v>2.212947</v>
       </c>
       <c r="N34">
-        <v>1.284112000000001</v>
+        <v>1.217053</v>
       </c>
       <c r="O34">
-        <v>0.1926168000000001</v>
+        <v>0.1825579500000001</v>
       </c>
       <c r="P34">
-        <v>1.091495200000001</v>
+        <v>1.03449505</v>
       </c>
       <c r="Q34">
-        <v>3.601495200000001</v>
+        <v>3.544495050000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09133381487401188</v>
+        <v>0.09194060878224765</v>
       </c>
       <c r="T34">
-        <v>0.8637596423744482</v>
+        <v>0.8752702985894596</v>
       </c>
       <c r="U34">
         <v>0.09</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.598405881388032</v>
+        <v>1.549969339527788</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08684520788410592</v>
+        <v>0.08710342165388377</v>
       </c>
       <c r="C35">
-        <v>39.01154268810032</v>
+        <v>37.99137188778423</v>
       </c>
       <c r="D35">
-        <v>43.99984268810032</v>
+        <v>43.72477188778423</v>
       </c>
       <c r="E35">
-        <v>18.3783</v>
+        <v>19.1234</v>
       </c>
       <c r="F35">
-        <v>24.5883</v>
+        <v>25.3334</v>
       </c>
       <c r="G35">
         <v>19.6</v>
@@ -4157,28 +4157,28 @@
         <v>3.43</v>
       </c>
       <c r="M35">
-        <v>2.212947</v>
+        <v>2.280006</v>
       </c>
       <c r="N35">
-        <v>1.217053</v>
+        <v>1.149994</v>
       </c>
       <c r="O35">
-        <v>0.1825579500000001</v>
+        <v>0.1724991</v>
       </c>
       <c r="P35">
-        <v>1.03449505</v>
+        <v>0.9774949000000004</v>
       </c>
       <c r="Q35">
-        <v>3.544495050000001</v>
+        <v>3.487494900000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09194060878224765</v>
+        <v>0.09256579038467239</v>
       </c>
       <c r="T35">
-        <v>0.8752702985894596</v>
+        <v>0.8871297625685622</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.549969339527788</v>
+        <v>1.504382006012265</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08710342165388377</v>
+        <v>0.1052391833417196</v>
       </c>
       <c r="C36">
-        <v>37.99137188778423</v>
+        <v>23.90520631067268</v>
       </c>
       <c r="D36">
-        <v>43.72477188778423</v>
+        <v>30.38370631067268</v>
       </c>
       <c r="E36">
-        <v>19.1234</v>
+        <v>19.8685</v>
       </c>
       <c r="F36">
-        <v>25.3334</v>
+        <v>26.0785</v>
       </c>
       <c r="G36">
         <v>19.6</v>
@@ -4239,45 +4239,45 @@
         <v>3.43</v>
       </c>
       <c r="M36">
-        <v>2.280006</v>
+        <v>3.8283238</v>
       </c>
       <c r="N36">
-        <v>1.149994</v>
+        <v>-0.3983238</v>
       </c>
       <c r="O36">
-        <v>0.1724991</v>
+        <v>-0.05974857</v>
       </c>
       <c r="P36">
-        <v>0.9774949000000004</v>
+        <v>-0.33857523</v>
       </c>
       <c r="Q36">
-        <v>3.487494900000001</v>
+        <v>2.17142477</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09256579038467239</v>
+        <v>0.09348353346048596</v>
       </c>
       <c r="T36">
-        <v>0.8871297625685622</v>
+        <v>0.9045390095896985</v>
       </c>
       <c r="U36">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.15</v>
+        <v>0.1343930207784409</v>
       </c>
       <c r="W36">
-        <v>0.0765</v>
+        <v>0.1270711045497249</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.504382006012265</v>
+        <v>0.8959534718562729</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1052391833417196</v>
+        <v>0.1062491833417196</v>
       </c>
       <c r="C37">
-        <v>23.90520631067268</v>
+        <v>22.6524477836699</v>
       </c>
       <c r="D37">
-        <v>30.38370631067268</v>
+        <v>29.87604778366989</v>
       </c>
       <c r="E37">
-        <v>19.8685</v>
+        <v>20.6136</v>
       </c>
       <c r="F37">
-        <v>26.0785</v>
+        <v>26.8236</v>
       </c>
       <c r="G37">
         <v>19.6</v>
@@ -4321,37 +4321,37 @@
         <v>3.43</v>
       </c>
       <c r="M37">
-        <v>3.8283238</v>
+        <v>3.93770448</v>
       </c>
       <c r="N37">
-        <v>-0.3983238</v>
+        <v>-0.5077044800000001</v>
       </c>
       <c r="O37">
-        <v>-0.05974857</v>
+        <v>-0.07615567200000002</v>
       </c>
       <c r="P37">
-        <v>-0.33857523</v>
+        <v>-0.4315488080000001</v>
       </c>
       <c r="Q37">
-        <v>2.17142477</v>
+        <v>2.078451192</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09348353346048596</v>
+        <v>0.09422858867080605</v>
       </c>
       <c r="T37">
-        <v>0.9045390095896985</v>
+        <v>0.9186724316145374</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.1343930207784409</v>
+        <v>0.1306598813123731</v>
       </c>
       <c r="W37">
-        <v>0.1270711045497249</v>
+        <v>0.1276191294233436</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8959534718562729</v>
+        <v>0.8710658754158209</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1062491833417196</v>
+        <v>0.1072591833417196</v>
       </c>
       <c r="C38">
-        <v>22.65244778366989</v>
+        <v>21.41637464311038</v>
       </c>
       <c r="D38">
-        <v>29.87604778366988</v>
+        <v>29.38507464311038</v>
       </c>
       <c r="E38">
-        <v>20.61359999999999</v>
+        <v>21.3587</v>
       </c>
       <c r="F38">
-        <v>26.8236</v>
+        <v>27.5687</v>
       </c>
       <c r="G38">
         <v>19.6</v>
@@ -4403,37 +4403,37 @@
         <v>3.43</v>
       </c>
       <c r="M38">
-        <v>3.93770448</v>
+        <v>4.04708516</v>
       </c>
       <c r="N38">
-        <v>-0.5077044799999997</v>
+        <v>-0.6170851599999998</v>
       </c>
       <c r="O38">
-        <v>-0.07615567199999995</v>
+        <v>-0.09256277399999997</v>
       </c>
       <c r="P38">
-        <v>-0.4315488079999997</v>
+        <v>-0.5245223859999998</v>
       </c>
       <c r="Q38">
-        <v>2.078451192000001</v>
+        <v>1.985477614000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09422858867080605</v>
+        <v>0.0949972964274855</v>
       </c>
       <c r="T38">
-        <v>0.9186724316145374</v>
+        <v>0.933254533703657</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.1306598813123732</v>
+        <v>0.1271285331687955</v>
       </c>
       <c r="W38">
-        <v>0.1276191294233436</v>
+        <v>0.1281375313308208</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.871065875415821</v>
+        <v>0.8475235544586366</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1072591833417196</v>
+        <v>0.1082691833417196</v>
       </c>
       <c r="C39">
-        <v>21.41637464311038</v>
+        <v>20.1961775824174</v>
       </c>
       <c r="D39">
-        <v>29.38507464311038</v>
+        <v>28.9099775824174</v>
       </c>
       <c r="E39">
-        <v>21.3587</v>
+        <v>22.1038</v>
       </c>
       <c r="F39">
-        <v>27.5687</v>
+        <v>28.3138</v>
       </c>
       <c r="G39">
         <v>19.6</v>
@@ -4485,37 +4485,37 @@
         <v>3.43</v>
       </c>
       <c r="M39">
-        <v>4.04708516</v>
+        <v>4.15646584</v>
       </c>
       <c r="N39">
-        <v>-0.6170851599999998</v>
+        <v>-0.7264658399999999</v>
       </c>
       <c r="O39">
-        <v>-0.09256277399999997</v>
+        <v>-0.108969876</v>
       </c>
       <c r="P39">
-        <v>-0.5245223859999998</v>
+        <v>-0.617495964</v>
       </c>
       <c r="Q39">
-        <v>1.985477614000001</v>
+        <v>1.892504036</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0949972964274855</v>
+        <v>0.09579080120857399</v>
       </c>
       <c r="T39">
-        <v>0.933254533703657</v>
+        <v>0.9483070261827483</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.1271285331687955</v>
+        <v>0.1237830454538272</v>
       </c>
       <c r="W39">
-        <v>0.1281375313308208</v>
+        <v>0.1286286489273782</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8475235544586366</v>
+        <v>0.8252203030255146</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1082691833417196</v>
+        <v>0.1092791833417196</v>
       </c>
       <c r="C40">
-        <v>20.1961775824174</v>
+        <v>18.99109880164044</v>
       </c>
       <c r="D40">
-        <v>28.9099775824174</v>
+        <v>28.44999880164044</v>
       </c>
       <c r="E40">
-        <v>22.1038</v>
+        <v>22.8489</v>
       </c>
       <c r="F40">
-        <v>28.3138</v>
+        <v>29.0589</v>
       </c>
       <c r="G40">
         <v>19.6</v>
@@ -4567,37 +4567,37 @@
         <v>3.43</v>
       </c>
       <c r="M40">
-        <v>4.15646584</v>
+        <v>4.26584652</v>
       </c>
       <c r="N40">
-        <v>-0.7264658399999999</v>
+        <v>-0.83584652</v>
       </c>
       <c r="O40">
-        <v>-0.108969876</v>
+        <v>-0.125376978</v>
       </c>
       <c r="P40">
-        <v>-0.617495964</v>
+        <v>-0.710469542</v>
       </c>
       <c r="Q40">
-        <v>1.892504036</v>
+        <v>1.799530458</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09579080120857399</v>
+        <v>0.09661032253986207</v>
       </c>
       <c r="T40">
-        <v>0.9483070261827483</v>
+        <v>0.9638530430054163</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.1237830454538272</v>
+        <v>0.1206091212114214</v>
       </c>
       <c r="W40">
-        <v>0.1286286489273782</v>
+        <v>0.1290945810061634</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8252203030255146</v>
+        <v>0.8040608080761424</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1092791833417196</v>
+        <v>0.1323005989967721</v>
       </c>
       <c r="C41">
-        <v>18.99109880164044</v>
+        <v>10.67426802295818</v>
       </c>
       <c r="D41">
-        <v>28.44999880164044</v>
+        <v>20.87826802295818</v>
       </c>
       <c r="E41">
-        <v>22.8489</v>
+        <v>23.594</v>
       </c>
       <c r="F41">
-        <v>29.0589</v>
+        <v>29.804</v>
       </c>
       <c r="G41">
         <v>19.6</v>
@@ -4649,45 +4649,45 @@
         <v>3.43</v>
       </c>
       <c r="M41">
-        <v>4.26584652</v>
+        <v>5.9846432</v>
       </c>
       <c r="N41">
-        <v>-0.83584652</v>
+        <v>-2.5546432</v>
       </c>
       <c r="O41">
-        <v>-0.125376978</v>
+        <v>-0.38319648</v>
       </c>
       <c r="P41">
-        <v>-0.710469542</v>
+        <v>-2.17144672</v>
       </c>
       <c r="Q41">
-        <v>1.799530458</v>
+        <v>0.3385532800000006</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09661032253986207</v>
+        <v>0.09814285400728064</v>
       </c>
       <c r="T41">
-        <v>0.9638530430054163</v>
+        <v>0.9929245986369335</v>
       </c>
       <c r="U41">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1206091212114214</v>
+        <v>0.08597003744517302</v>
       </c>
       <c r="W41">
-        <v>0.1290945810061634</v>
+        <v>0.1835372164810093</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.8040608080761424</v>
+        <v>0.5731335829678201</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1323005989967721</v>
+        <v>0.1338505989967721</v>
       </c>
       <c r="C42">
-        <v>10.67426802295818</v>
+        <v>9.561637128173796</v>
       </c>
       <c r="D42">
-        <v>20.87826802295818</v>
+        <v>20.51073712817379</v>
       </c>
       <c r="E42">
-        <v>23.594</v>
+        <v>24.3391</v>
       </c>
       <c r="F42">
-        <v>29.804</v>
+        <v>30.5491</v>
       </c>
       <c r="G42">
         <v>19.6</v>
@@ -4731,37 +4731,37 @@
         <v>3.43</v>
       </c>
       <c r="M42">
-        <v>5.9846432</v>
+        <v>6.13425928</v>
       </c>
       <c r="N42">
-        <v>-2.5546432</v>
+        <v>-2.70425928</v>
       </c>
       <c r="O42">
-        <v>-0.38319648</v>
+        <v>-0.405638892</v>
       </c>
       <c r="P42">
-        <v>-2.17144672</v>
+        <v>-2.298620388</v>
       </c>
       <c r="Q42">
-        <v>0.3385532800000006</v>
+        <v>0.211379612</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09814285400728064</v>
+        <v>0.09903002102435318</v>
       </c>
       <c r="T42">
-        <v>0.9929245986369335</v>
+        <v>1.009753829122305</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.08597003744517302</v>
+        <v>0.08387320726358342</v>
       </c>
       <c r="W42">
-        <v>0.1835372164810093</v>
+        <v>0.1839582599814725</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5731335829678201</v>
+        <v>0.5591547150905561</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1338505989967721</v>
+        <v>0.1354005989967721</v>
       </c>
       <c r="C43">
-        <v>9.561637128173796</v>
+        <v>8.46172206103552</v>
       </c>
       <c r="D43">
-        <v>20.51073712817379</v>
+        <v>20.15592206103551</v>
       </c>
       <c r="E43">
-        <v>24.3391</v>
+        <v>25.0842</v>
       </c>
       <c r="F43">
-        <v>30.5491</v>
+        <v>31.2942</v>
       </c>
       <c r="G43">
         <v>19.6</v>
@@ -4813,37 +4813,37 @@
         <v>3.43</v>
       </c>
       <c r="M43">
-        <v>6.13425928</v>
+        <v>6.283875360000001</v>
       </c>
       <c r="N43">
-        <v>-2.70425928</v>
+        <v>-2.85387536</v>
       </c>
       <c r="O43">
-        <v>-0.405638892</v>
+        <v>-0.4280813040000001</v>
       </c>
       <c r="P43">
-        <v>-2.298620388</v>
+        <v>-2.425794056</v>
       </c>
       <c r="Q43">
-        <v>0.211379612</v>
+        <v>0.08420594399999981</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09903002102435318</v>
+        <v>0.09994778000753168</v>
       </c>
       <c r="T43">
-        <v>1.009753829122305</v>
+        <v>1.027163377900276</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.08387320726358342</v>
+        <v>0.08187622613826</v>
       </c>
       <c r="W43">
-        <v>0.1839582599814725</v>
+        <v>0.1843592537914374</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5591547150905561</v>
+        <v>0.5458415075884</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1354005989967721</v>
+        <v>0.1369505989967721</v>
       </c>
       <c r="C44">
-        <v>8.461722061035523</v>
+        <v>7.373874130265349</v>
       </c>
       <c r="D44">
-        <v>20.15592206103551</v>
+        <v>19.81317413026535</v>
       </c>
       <c r="E44">
-        <v>25.0842</v>
+        <v>25.8293</v>
       </c>
       <c r="F44">
-        <v>31.2942</v>
+        <v>32.0393</v>
       </c>
       <c r="G44">
         <v>19.6</v>
@@ -4895,37 +4895,37 @@
         <v>3.43</v>
       </c>
       <c r="M44">
-        <v>6.28387536</v>
+        <v>6.43349144</v>
       </c>
       <c r="N44">
-        <v>-2.85387536</v>
+        <v>-3.00349144</v>
       </c>
       <c r="O44">
-        <v>-0.4280813039999999</v>
+        <v>-0.450523716</v>
       </c>
       <c r="P44">
-        <v>-2.425794056</v>
+        <v>-2.552967724</v>
       </c>
       <c r="Q44">
-        <v>0.0842059440000007</v>
+        <v>-0.04296772399999993</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09994778000753168</v>
+        <v>0.1008977410602954</v>
       </c>
       <c r="T44">
-        <v>1.027163377900276</v>
+        <v>1.045183788038877</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.08187622613826001</v>
+        <v>0.07997212785597489</v>
       </c>
       <c r="W44">
-        <v>0.1843592537914374</v>
+        <v>0.1847415967265203</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5458415075884001</v>
+        <v>0.5331475190398326</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1369505989967721</v>
+        <v>0.1385005989967721</v>
       </c>
       <c r="C45">
-        <v>7.373874130265349</v>
+        <v>6.297488030345107</v>
       </c>
       <c r="D45">
-        <v>19.81317413026535</v>
+        <v>19.4818880303451</v>
       </c>
       <c r="E45">
-        <v>25.8293</v>
+        <v>26.5744</v>
       </c>
       <c r="F45">
-        <v>32.0393</v>
+        <v>32.7844</v>
       </c>
       <c r="G45">
         <v>19.6</v>
@@ -4977,37 +4977,37 @@
         <v>3.43</v>
       </c>
       <c r="M45">
-        <v>6.43349144</v>
+        <v>6.58310752</v>
       </c>
       <c r="N45">
-        <v>-3.00349144</v>
+        <v>-3.153107519999999</v>
       </c>
       <c r="O45">
-        <v>-0.450523716</v>
+        <v>-0.4729661279999999</v>
       </c>
       <c r="P45">
-        <v>-2.552967724</v>
+        <v>-2.680141391999999</v>
       </c>
       <c r="Q45">
-        <v>-0.04296772399999993</v>
+        <v>-0.1701413919999992</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1008977410602954</v>
+        <v>0.101881629293515</v>
       </c>
       <c r="T45">
-        <v>1.045183788038877</v>
+        <v>1.063847784253857</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.07997212785597489</v>
+        <v>0.07815457949561182</v>
       </c>
       <c r="W45">
-        <v>0.1847415967265203</v>
+        <v>0.1851065604372812</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5331475190398326</v>
+        <v>0.5210305299707456</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1385005989967721</v>
+        <v>0.1400505989967721</v>
       </c>
       <c r="C46">
-        <v>6.297488030345107</v>
+        <v>5.231998274009769</v>
       </c>
       <c r="D46">
-        <v>19.4818880303451</v>
+        <v>19.16149827400977</v>
       </c>
       <c r="E46">
-        <v>26.5744</v>
+        <v>27.3195</v>
       </c>
       <c r="F46">
-        <v>32.7844</v>
+        <v>33.5295</v>
       </c>
       <c r="G46">
         <v>19.6</v>
@@ -5059,37 +5059,37 @@
         <v>3.43</v>
       </c>
       <c r="M46">
-        <v>6.58310752</v>
+        <v>6.7327236</v>
       </c>
       <c r="N46">
-        <v>-3.153107519999999</v>
+        <v>-3.3027236</v>
       </c>
       <c r="O46">
-        <v>-0.4729661279999999</v>
+        <v>-0.49540854</v>
       </c>
       <c r="P46">
-        <v>-2.680141391999999</v>
+        <v>-2.80731506</v>
       </c>
       <c r="Q46">
-        <v>-0.1701413919999992</v>
+        <v>-0.2973150599999994</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.101881629293515</v>
+        <v>0.1029012952806698</v>
       </c>
       <c r="T46">
-        <v>1.063847784253857</v>
+        <v>1.083190471240291</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.07815457949561182</v>
+        <v>0.07641781106237601</v>
       </c>
       <c r="W46">
-        <v>0.1851065604372812</v>
+        <v>0.1854553035386749</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5210305299707456</v>
+        <v>0.5094520737491735</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1400505989967721</v>
+        <v>0.1578666101829358</v>
       </c>
       <c r="C47">
-        <v>5.231998274009769</v>
+        <v>1.44066115631567</v>
       </c>
       <c r="D47">
-        <v>19.16149827400977</v>
+        <v>16.11526115631567</v>
       </c>
       <c r="E47">
-        <v>27.3195</v>
+        <v>28.0646</v>
       </c>
       <c r="F47">
-        <v>33.5295</v>
+        <v>34.2746</v>
       </c>
       <c r="G47">
         <v>19.6</v>
@@ -5141,45 +5141,45 @@
         <v>3.43</v>
       </c>
       <c r="M47">
-        <v>6.7327236</v>
+        <v>8.08195068</v>
       </c>
       <c r="N47">
-        <v>-3.3027236</v>
+        <v>-4.651950680000001</v>
       </c>
       <c r="O47">
-        <v>-0.49540854</v>
+        <v>-0.697792602</v>
       </c>
       <c r="P47">
-        <v>-2.80731506</v>
+        <v>-3.954158078000001</v>
       </c>
       <c r="Q47">
-        <v>-0.2973150599999994</v>
+        <v>-1.444158078000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1029012952806698</v>
+        <v>0.1042661547972817</v>
       </c>
       <c r="T47">
-        <v>1.083190471240291</v>
+        <v>1.109081351923624</v>
       </c>
       <c r="U47">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.07641781106237601</v>
+        <v>0.06366037363643005</v>
       </c>
       <c r="W47">
-        <v>0.1854553035386749</v>
+        <v>0.2207888838965298</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.5094520737491735</v>
+        <v>0.4244024909095336</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1578666101829358</v>
+        <v>0.1597666101829358</v>
       </c>
       <c r="C48">
-        <v>1.44066115631567</v>
+        <v>0.4268947798405662</v>
       </c>
       <c r="D48">
-        <v>16.11526115631567</v>
+        <v>15.84659477984056</v>
       </c>
       <c r="E48">
-        <v>28.0646</v>
+        <v>28.8097</v>
       </c>
       <c r="F48">
-        <v>34.2746</v>
+        <v>35.0197</v>
       </c>
       <c r="G48">
         <v>19.6</v>
@@ -5223,37 +5223,37 @@
         <v>3.43</v>
       </c>
       <c r="M48">
-        <v>8.08195068</v>
+        <v>8.25764526</v>
       </c>
       <c r="N48">
-        <v>-4.651950680000001</v>
+        <v>-4.827645260000001</v>
       </c>
       <c r="O48">
-        <v>-0.697792602</v>
+        <v>-0.7241467890000001</v>
       </c>
       <c r="P48">
-        <v>-3.954158078000001</v>
+        <v>-4.103498471000001</v>
       </c>
       <c r="Q48">
-        <v>-1.444158078000001</v>
+        <v>-1.593498471000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1042661547972817</v>
+        <v>0.1053692897934568</v>
       </c>
       <c r="T48">
-        <v>1.109081351923624</v>
+        <v>1.130007415167466</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.06366037363643005</v>
+        <v>0.0623058976016124</v>
       </c>
       <c r="W48">
-        <v>0.2207888838965298</v>
+        <v>0.2211082693455398</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4244024909095336</v>
+        <v>0.4153726506774159</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1597666101829358</v>
+        <v>0.1616666101829358</v>
       </c>
       <c r="C49">
-        <v>0.4268947798405662</v>
+        <v>-0.578060324526092</v>
       </c>
       <c r="D49">
-        <v>15.84659477984056</v>
+        <v>15.58673967547391</v>
       </c>
       <c r="E49">
-        <v>28.8097</v>
+        <v>29.5548</v>
       </c>
       <c r="F49">
-        <v>35.0197</v>
+        <v>35.7648</v>
       </c>
       <c r="G49">
         <v>19.6</v>
@@ -5305,37 +5305,37 @@
         <v>3.43</v>
       </c>
       <c r="M49">
-        <v>8.25764526</v>
+        <v>8.43333984</v>
       </c>
       <c r="N49">
-        <v>-4.827645260000001</v>
+        <v>-5.003339840000001</v>
       </c>
       <c r="O49">
-        <v>-0.7241467890000001</v>
+        <v>-0.7505009760000001</v>
       </c>
       <c r="P49">
-        <v>-4.103498471000001</v>
+        <v>-4.252838864000001</v>
       </c>
       <c r="Q49">
-        <v>-1.593498471000001</v>
+        <v>-1.742838864000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1053692897934568</v>
+        <v>0.1065148530587156</v>
       </c>
       <c r="T49">
-        <v>1.130007415167466</v>
+        <v>1.15173832699761</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.0623058976016124</v>
+        <v>0.06100785806824547</v>
       </c>
       <c r="W49">
-        <v>0.2211082693455398</v>
+        <v>0.2214143470675077</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4153726506774159</v>
+        <v>0.4067190537883031</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1616666101829358</v>
+        <v>0.1635666101829358</v>
       </c>
       <c r="C50">
-        <v>-0.5780603245260778</v>
+        <v>-1.574630629542057</v>
       </c>
       <c r="D50">
-        <v>15.58673967547391</v>
+        <v>15.33526937045794</v>
       </c>
       <c r="E50">
-        <v>29.55479999999999</v>
+        <v>30.29989999999999</v>
       </c>
       <c r="F50">
-        <v>35.76479999999999</v>
+        <v>36.50989999999999</v>
       </c>
       <c r="G50">
         <v>19.6</v>
@@ -5387,37 +5387,37 @@
         <v>3.43</v>
       </c>
       <c r="M50">
-        <v>8.433339839999999</v>
+        <v>8.609034419999999</v>
       </c>
       <c r="N50">
-        <v>-5.003339839999999</v>
+        <v>-5.179034419999999</v>
       </c>
       <c r="O50">
-        <v>-0.7505009759999998</v>
+        <v>-0.7768551629999998</v>
       </c>
       <c r="P50">
-        <v>-4.252838863999999</v>
+        <v>-4.402179256999999</v>
       </c>
       <c r="Q50">
-        <v>-1.742838863999999</v>
+        <v>-1.892179256999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1065148530587156</v>
+        <v>0.1077053403735923</v>
       </c>
       <c r="T50">
-        <v>1.15173832699761</v>
+        <v>1.174321431448544</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.06100785806824548</v>
+        <v>0.05976279974032211</v>
       </c>
       <c r="W50">
-        <v>0.2214143470675077</v>
+        <v>0.2217079318212321</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4067190537883032</v>
+        <v>0.3984186649354807</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1635666101829358</v>
+        <v>0.1654666101829358</v>
       </c>
       <c r="C51">
-        <v>-1.574630629542057</v>
+        <v>-2.563215522774414</v>
       </c>
       <c r="D51">
-        <v>15.33526937045794</v>
+        <v>15.09178447722558</v>
       </c>
       <c r="E51">
-        <v>30.29989999999999</v>
+        <v>31.04499999999999</v>
       </c>
       <c r="F51">
-        <v>36.50989999999999</v>
+        <v>37.255</v>
       </c>
       <c r="G51">
         <v>19.6</v>
@@ -5469,37 +5469,37 @@
         <v>3.43</v>
       </c>
       <c r="M51">
-        <v>8.609034419999999</v>
+        <v>8.784728999999999</v>
       </c>
       <c r="N51">
-        <v>-5.179034419999999</v>
+        <v>-5.354728999999999</v>
       </c>
       <c r="O51">
-        <v>-0.7768551629999998</v>
+        <v>-0.8032093499999998</v>
       </c>
       <c r="P51">
-        <v>-4.402179256999999</v>
+        <v>-4.551519649999999</v>
       </c>
       <c r="Q51">
-        <v>-1.892179256999999</v>
+        <v>-2.041519649999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1077053403735923</v>
+        <v>0.1089434471810642</v>
       </c>
       <c r="T51">
-        <v>1.174321431448544</v>
+        <v>1.197807860077514</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05976279974032211</v>
+        <v>0.05856754374551567</v>
       </c>
       <c r="W51">
-        <v>0.2217079318212321</v>
+        <v>0.2219897731848074</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3984186649354807</v>
+        <v>0.390450291636771</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1654666101829358</v>
+        <v>0.1673666101829358</v>
       </c>
       <c r="C52">
-        <v>-2.563215522774414</v>
+        <v>-3.544189423211208</v>
       </c>
       <c r="D52">
-        <v>15.09178447722558</v>
+        <v>14.85591057678879</v>
       </c>
       <c r="E52">
-        <v>31.04499999999999</v>
+        <v>31.7901</v>
       </c>
       <c r="F52">
-        <v>37.255</v>
+        <v>38.0001</v>
       </c>
       <c r="G52">
         <v>19.6</v>
@@ -5551,37 +5551,37 @@
         <v>3.43</v>
       </c>
       <c r="M52">
-        <v>8.784728999999999</v>
+        <v>8.960423579999999</v>
       </c>
       <c r="N52">
-        <v>-5.354728999999999</v>
+        <v>-5.530423579999999</v>
       </c>
       <c r="O52">
-        <v>-0.8032093499999998</v>
+        <v>-0.8295635369999999</v>
       </c>
       <c r="P52">
-        <v>-4.551519649999999</v>
+        <v>-4.700860042999999</v>
       </c>
       <c r="Q52">
-        <v>-2.041519649999999</v>
+        <v>-2.190860042999998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1089434471810642</v>
+        <v>0.1102320889602696</v>
       </c>
       <c r="T52">
-        <v>1.197807860077514</v>
+        <v>1.222252918446443</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05856754374551567</v>
+        <v>0.05741916053481928</v>
       </c>
       <c r="W52">
-        <v>0.2219897731848074</v>
+        <v>0.2222605619458896</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.390450291636771</v>
+        <v>0.3827944035654618</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1673666101829358</v>
+        <v>0.1692666101829358</v>
       </c>
       <c r="C53">
-        <v>-3.544189423211208</v>
+        <v>-4.517903702440854</v>
       </c>
       <c r="D53">
-        <v>14.85591057678879</v>
+        <v>14.62729629755914</v>
       </c>
       <c r="E53">
-        <v>31.7901</v>
+        <v>32.5352</v>
       </c>
       <c r="F53">
-        <v>38.0001</v>
+        <v>38.7452</v>
       </c>
       <c r="G53">
         <v>19.6</v>
@@ -5633,37 +5633,37 @@
         <v>3.43</v>
       </c>
       <c r="M53">
-        <v>8.960423579999999</v>
+        <v>9.136118160000001</v>
       </c>
       <c r="N53">
-        <v>-5.530423579999999</v>
+        <v>-5.706118160000001</v>
       </c>
       <c r="O53">
-        <v>-0.8295635369999999</v>
+        <v>-0.8559177240000001</v>
       </c>
       <c r="P53">
-        <v>-4.700860042999999</v>
+        <v>-4.850200436000001</v>
       </c>
       <c r="Q53">
-        <v>-2.190860042999998</v>
+        <v>-2.340200436</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1102320889602696</v>
+        <v>0.1115744241469419</v>
       </c>
       <c r="T53">
-        <v>1.222252918446443</v>
+        <v>1.247716520914078</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05741916053481928</v>
+        <v>0.05631494590914966</v>
       </c>
       <c r="W53">
-        <v>0.2222605619458896</v>
+        <v>0.2225209357546225</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3827944035654618</v>
+        <v>0.3754329727276644</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1692666101829358</v>
+        <v>0.1711666101829358</v>
       </c>
       <c r="C54">
-        <v>-4.517903702440854</v>
+        <v>-5.484688431132234</v>
       </c>
       <c r="D54">
-        <v>14.62729629755914</v>
+        <v>14.40561156886777</v>
       </c>
       <c r="E54">
-        <v>32.5352</v>
+        <v>33.2803</v>
       </c>
       <c r="F54">
-        <v>38.7452</v>
+        <v>39.4903</v>
       </c>
       <c r="G54">
         <v>19.6</v>
@@ -5715,37 +5715,37 @@
         <v>3.43</v>
       </c>
       <c r="M54">
-        <v>9.136118160000001</v>
+        <v>9.311812740000001</v>
       </c>
       <c r="N54">
-        <v>-5.706118160000001</v>
+        <v>-5.881812740000001</v>
       </c>
       <c r="O54">
-        <v>-0.8559177240000001</v>
+        <v>-0.8822719110000001</v>
       </c>
       <c r="P54">
-        <v>-4.850200436000001</v>
+        <v>-4.999540829000001</v>
       </c>
       <c r="Q54">
-        <v>-2.340200436</v>
+        <v>-2.489540829000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1115744241469419</v>
+        <v>0.1129738799798555</v>
       </c>
       <c r="T54">
-        <v>1.247716520914078</v>
+        <v>1.274263680933526</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05631494590914966</v>
+        <v>0.05525239975992043</v>
       </c>
       <c r="W54">
-        <v>0.2225209357546225</v>
+        <v>0.2227714841366108</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3754329727276644</v>
+        <v>0.3683493317328028</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1711666101829358</v>
+        <v>0.1730666101829358</v>
       </c>
       <c r="C55">
-        <v>-5.484688431132234</v>
+        <v>-6.444853969072668</v>
       </c>
       <c r="D55">
-        <v>14.40561156886777</v>
+        <v>14.19054603092733</v>
       </c>
       <c r="E55">
-        <v>33.2803</v>
+        <v>34.0254</v>
       </c>
       <c r="F55">
-        <v>39.4903</v>
+        <v>40.2354</v>
       </c>
       <c r="G55">
         <v>19.6</v>
@@ -5797,37 +5797,37 @@
         <v>3.43</v>
       </c>
       <c r="M55">
-        <v>9.311812740000001</v>
+        <v>9.487507320000001</v>
       </c>
       <c r="N55">
-        <v>-5.881812740000001</v>
+        <v>-6.057507320000001</v>
       </c>
       <c r="O55">
-        <v>-0.8822719110000001</v>
+        <v>-0.908626098</v>
       </c>
       <c r="P55">
-        <v>-4.999540829000001</v>
+        <v>-5.148881222000001</v>
       </c>
       <c r="Q55">
-        <v>-2.489540829000001</v>
+        <v>-2.638881222000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1129738799798555</v>
+        <v>0.114434181718548</v>
       </c>
       <c r="T55">
-        <v>1.274263680933526</v>
+        <v>1.301965065301646</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05525239975992043</v>
+        <v>0.05422920717177375</v>
       </c>
       <c r="W55">
-        <v>0.2227714841366108</v>
+        <v>0.2230127529488958</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3683493317328028</v>
+        <v>0.361528047811825</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1730666101829358</v>
+        <v>0.1749666101829358</v>
       </c>
       <c r="C56">
-        <v>-6.444853969072668</v>
+        <v>-7.398692414872059</v>
       </c>
       <c r="D56">
-        <v>14.19054603092733</v>
+        <v>13.98180758512794</v>
       </c>
       <c r="E56">
-        <v>34.0254</v>
+        <v>34.7705</v>
       </c>
       <c r="F56">
-        <v>40.2354</v>
+        <v>40.9805</v>
       </c>
       <c r="G56">
         <v>19.6</v>
@@ -5879,37 +5879,37 @@
         <v>3.43</v>
       </c>
       <c r="M56">
-        <v>9.487507320000001</v>
+        <v>9.663201900000001</v>
       </c>
       <c r="N56">
-        <v>-6.057507320000001</v>
+        <v>-6.233201900000001</v>
       </c>
       <c r="O56">
-        <v>-0.908626098</v>
+        <v>-0.9349802850000001</v>
       </c>
       <c r="P56">
-        <v>-5.148881222000001</v>
+        <v>-5.298221615000001</v>
       </c>
       <c r="Q56">
-        <v>-2.638881222000001</v>
+        <v>-2.788221615000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.114434181718548</v>
+        <v>0.115959385756738</v>
       </c>
       <c r="T56">
-        <v>1.301965065301646</v>
+        <v>1.33089762230835</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05422920717177375</v>
+        <v>0.05324322158683241</v>
       </c>
       <c r="W56">
-        <v>0.2230127529488958</v>
+        <v>0.2232452483498249</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.361528047811825</v>
+        <v>0.3549548105788827</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1749666101829358</v>
+        <v>0.1768666101829358</v>
       </c>
       <c r="C57">
-        <v>-7.398692414872059</v>
+        <v>-8.346478929573749</v>
       </c>
       <c r="D57">
-        <v>13.98180758512794</v>
+        <v>13.77912107042625</v>
       </c>
       <c r="E57">
-        <v>34.7705</v>
+        <v>35.5156</v>
       </c>
       <c r="F57">
-        <v>40.9805</v>
+        <v>41.7256</v>
       </c>
       <c r="G57">
         <v>19.6</v>
@@ -5961,37 +5961,37 @@
         <v>3.43</v>
       </c>
       <c r="M57">
-        <v>9.663201900000001</v>
+        <v>9.838896480000001</v>
       </c>
       <c r="N57">
-        <v>-6.233201900000001</v>
+        <v>-6.408896480000001</v>
       </c>
       <c r="O57">
-        <v>-0.9349802850000001</v>
+        <v>-0.9613344720000001</v>
       </c>
       <c r="P57">
-        <v>-5.298221615000001</v>
+        <v>-5.447562008000001</v>
       </c>
       <c r="Q57">
-        <v>-2.788221615000001</v>
+        <v>-2.937562008000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.115959385756738</v>
+        <v>0.1175539172512093</v>
       </c>
       <c r="T57">
-        <v>1.33089762230835</v>
+        <v>1.36114529554263</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05324322158683241</v>
+        <v>0.05229244977278184</v>
       </c>
       <c r="W57">
-        <v>0.2232452483498249</v>
+        <v>0.2234694403435781</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3549548105788827</v>
+        <v>0.3486163318185456</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1768666101829358</v>
+        <v>0.1787666101829358</v>
       </c>
       <c r="C58">
-        <v>-8.346478929573749</v>
+        <v>-9.288472946784459</v>
       </c>
       <c r="D58">
-        <v>13.77912107042625</v>
+        <v>13.58222705321554</v>
       </c>
       <c r="E58">
-        <v>35.5156</v>
+        <v>36.2607</v>
       </c>
       <c r="F58">
-        <v>41.7256</v>
+        <v>42.4707</v>
       </c>
       <c r="G58">
         <v>19.6</v>
@@ -6043,37 +6043,37 @@
         <v>3.43</v>
       </c>
       <c r="M58">
-        <v>9.838896480000001</v>
+        <v>10.01459106</v>
       </c>
       <c r="N58">
-        <v>-6.408896480000001</v>
+        <v>-6.584591060000001</v>
       </c>
       <c r="O58">
-        <v>-0.9613344720000001</v>
+        <v>-0.9876886590000001</v>
       </c>
       <c r="P58">
-        <v>-5.447562008000001</v>
+        <v>-5.596902401000001</v>
       </c>
       <c r="Q58">
-        <v>-2.937562008000001</v>
+        <v>-3.086902401000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1175539172512093</v>
+        <v>0.1192226130012375</v>
       </c>
       <c r="T58">
-        <v>1.36114529554263</v>
+        <v>1.392799837299436</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05229244977278184</v>
+        <v>0.05137503837325934</v>
       </c>
       <c r="W58">
-        <v>0.2234694403435781</v>
+        <v>0.2236857659515855</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3486163318185456</v>
+        <v>0.3425002558217289</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1787666101829358</v>
+        <v>0.1806666101829358</v>
       </c>
       <c r="C59">
-        <v>-9.288472946784459</v>
+        <v>-10.22491928051455</v>
       </c>
       <c r="D59">
-        <v>13.58222705321554</v>
+        <v>13.39088071948545</v>
       </c>
       <c r="E59">
-        <v>36.2607</v>
+        <v>37.0058</v>
       </c>
       <c r="F59">
-        <v>42.4707</v>
+        <v>43.2158</v>
       </c>
       <c r="G59">
         <v>19.6</v>
@@ -6125,37 +6125,37 @@
         <v>3.43</v>
       </c>
       <c r="M59">
-        <v>10.01459106</v>
+        <v>10.19028564</v>
       </c>
       <c r="N59">
-        <v>-6.584591060000001</v>
+        <v>-6.760285640000001</v>
       </c>
       <c r="O59">
-        <v>-0.9876886590000001</v>
+        <v>-1.014042846</v>
       </c>
       <c r="P59">
-        <v>-5.596902401000001</v>
+        <v>-5.746242794</v>
       </c>
       <c r="Q59">
-        <v>-3.086902401000001</v>
+        <v>-3.236242794</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1192226130012375</v>
+        <v>0.1209707704536478</v>
       </c>
       <c r="T59">
-        <v>1.392799837299436</v>
+        <v>1.425961738187517</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05137503837325934</v>
+        <v>0.05048926184958246</v>
       </c>
       <c r="W59">
-        <v>0.2236857659515855</v>
+        <v>0.2238946320558685</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3425002558217289</v>
+        <v>0.3365950789972163</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1806666101829358</v>
+        <v>0.1825666101829358</v>
       </c>
       <c r="C60">
-        <v>-10.22491928051454</v>
+        <v>-11.15604914067552</v>
       </c>
       <c r="D60">
-        <v>13.39088071948545</v>
+        <v>13.20485085932448</v>
       </c>
       <c r="E60">
-        <v>37.00579999999999</v>
+        <v>37.75089999999999</v>
       </c>
       <c r="F60">
-        <v>43.21579999999999</v>
+        <v>43.9609</v>
       </c>
       <c r="G60">
         <v>19.6</v>
@@ -6207,37 +6207,37 @@
         <v>3.43</v>
       </c>
       <c r="M60">
-        <v>10.19028564</v>
+        <v>10.36598022</v>
       </c>
       <c r="N60">
-        <v>-6.760285639999999</v>
+        <v>-6.935980219999999</v>
       </c>
       <c r="O60">
-        <v>-1.014042846</v>
+        <v>-1.040397033</v>
       </c>
       <c r="P60">
-        <v>-5.746242794</v>
+        <v>-5.895583187</v>
       </c>
       <c r="Q60">
-        <v>-3.236242793999999</v>
+        <v>-3.385583186999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1209707704536478</v>
+        <v>0.1228042038793466</v>
       </c>
       <c r="T60">
-        <v>1.425961738187517</v>
+        <v>1.460741292777457</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05048926184958247</v>
+        <v>0.04963351164874209</v>
       </c>
       <c r="W60">
-        <v>0.2238946320558685</v>
+        <v>0.2240964179532266</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3365950789972164</v>
+        <v>0.3308900776582805</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1825666101829358</v>
+        <v>0.1844666101829358</v>
       </c>
       <c r="C61">
-        <v>-11.15604914067552</v>
+        <v>-12.08208106509205</v>
       </c>
       <c r="D61">
-        <v>13.20485085932448</v>
+        <v>13.02391893490794</v>
       </c>
       <c r="E61">
-        <v>37.75089999999999</v>
+        <v>38.496</v>
       </c>
       <c r="F61">
-        <v>43.9609</v>
+        <v>44.706</v>
       </c>
       <c r="G61">
         <v>19.6</v>
@@ -6289,37 +6289,37 @@
         <v>3.43</v>
       </c>
       <c r="M61">
-        <v>10.36598022</v>
+        <v>10.5416748</v>
       </c>
       <c r="N61">
-        <v>-6.935980219999999</v>
+        <v>-7.111674799999999</v>
       </c>
       <c r="O61">
-        <v>-1.040397033</v>
+        <v>-1.06675122</v>
       </c>
       <c r="P61">
-        <v>-5.895583187</v>
+        <v>-6.04492358</v>
       </c>
       <c r="Q61">
-        <v>-3.385583186999999</v>
+        <v>-3.53492358</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1228042038793466</v>
+        <v>0.1247293089763302</v>
       </c>
       <c r="T61">
-        <v>1.460741292777457</v>
+        <v>1.497259825096893</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04963351164874209</v>
+        <v>0.04880628645459639</v>
       </c>
       <c r="W61">
-        <v>0.2240964179532266</v>
+        <v>0.2242914776540062</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3308900776582805</v>
+        <v>0.3253752430306426</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1844666101829358</v>
+        <v>0.1863666101829358</v>
       </c>
       <c r="C62">
-        <v>-12.08208106509205</v>
+        <v>-13.00322177592745</v>
       </c>
       <c r="D62">
-        <v>13.02391893490794</v>
+        <v>12.84787822407255</v>
       </c>
       <c r="E62">
-        <v>38.496</v>
+        <v>39.2411</v>
       </c>
       <c r="F62">
-        <v>44.706</v>
+        <v>45.4511</v>
       </c>
       <c r="G62">
         <v>19.6</v>
@@ -6371,37 +6371,37 @@
         <v>3.43</v>
       </c>
       <c r="M62">
-        <v>10.5416748</v>
+        <v>10.71736938</v>
       </c>
       <c r="N62">
-        <v>-7.111674799999999</v>
+        <v>-7.287369379999999</v>
       </c>
       <c r="O62">
-        <v>-1.06675122</v>
+        <v>-1.093105407</v>
       </c>
       <c r="P62">
-        <v>-6.04492358</v>
+        <v>-6.194263973</v>
       </c>
       <c r="Q62">
-        <v>-3.53492358</v>
+        <v>-3.684263973</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1247293089763302</v>
+        <v>0.1267531374116208</v>
       </c>
       <c r="T62">
-        <v>1.497259825096893</v>
+        <v>1.53565110266348</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04880628645459639</v>
+        <v>0.04800618339796366</v>
       </c>
       <c r="W62">
-        <v>0.2242914776540062</v>
+        <v>0.2244801419547602</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3253752430306426</v>
+        <v>0.320041222653091</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1863666101829358</v>
+        <v>0.1882666101829358</v>
       </c>
       <c r="C63">
-        <v>-13.00322177592745</v>
+        <v>-13.91966696757897</v>
       </c>
       <c r="D63">
-        <v>12.84787822407255</v>
+        <v>12.67653303242102</v>
       </c>
       <c r="E63">
-        <v>39.2411</v>
+        <v>39.9862</v>
       </c>
       <c r="F63">
-        <v>45.4511</v>
+        <v>46.1962</v>
       </c>
       <c r="G63">
         <v>19.6</v>
@@ -6453,37 +6453,37 @@
         <v>3.43</v>
       </c>
       <c r="M63">
-        <v>10.71736938</v>
+        <v>10.89306396</v>
       </c>
       <c r="N63">
-        <v>-7.287369379999999</v>
+        <v>-7.463063959999999</v>
       </c>
       <c r="O63">
-        <v>-1.093105407</v>
+        <v>-1.119459594</v>
       </c>
       <c r="P63">
-        <v>-6.194263973</v>
+        <v>-6.343604365999999</v>
       </c>
       <c r="Q63">
-        <v>-3.684263973</v>
+        <v>-3.833604365999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1267531374116208</v>
+        <v>0.1288834831329792</v>
       </c>
       <c r="T63">
-        <v>1.53565110266348</v>
+        <v>1.576062973786203</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04800618339796366</v>
+        <v>0.04723189011735134</v>
       </c>
       <c r="W63">
-        <v>0.2244801419547602</v>
+        <v>0.2246627203103286</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.320041222653091</v>
+        <v>0.3148792674490088</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1882666101829358</v>
+        <v>0.1901666101829358</v>
       </c>
       <c r="C64">
-        <v>-13.91966696757897</v>
+        <v>-14.83160203235662</v>
       </c>
       <c r="D64">
-        <v>12.67653303242102</v>
+        <v>12.50969796764337</v>
       </c>
       <c r="E64">
-        <v>39.9862</v>
+        <v>40.73129999999999</v>
       </c>
       <c r="F64">
-        <v>46.1962</v>
+        <v>46.94129999999999</v>
       </c>
       <c r="G64">
         <v>19.6</v>
@@ -6535,37 +6535,37 @@
         <v>3.43</v>
       </c>
       <c r="M64">
-        <v>10.89306396</v>
+        <v>11.06875854</v>
       </c>
       <c r="N64">
-        <v>-7.463063959999999</v>
+        <v>-7.638758539999998</v>
       </c>
       <c r="O64">
-        <v>-1.119459594</v>
+        <v>-1.145813781</v>
       </c>
       <c r="P64">
-        <v>-6.343604365999999</v>
+        <v>-6.492944758999998</v>
       </c>
       <c r="Q64">
-        <v>-3.833604365999999</v>
+        <v>-3.982944758999998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1288834831329792</v>
+        <v>0.1311289826771138</v>
       </c>
       <c r="T64">
-        <v>1.576062973786203</v>
+        <v>1.618659270375019</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04723189011735134</v>
+        <v>0.04648217757580609</v>
       </c>
       <c r="W64">
-        <v>0.2246627203103286</v>
+        <v>0.2248395025276249</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3148792674490088</v>
+        <v>0.3098811838387072</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1901666101829358</v>
+        <v>0.1920666101829358</v>
       </c>
       <c r="C65">
-        <v>-14.83160203235662</v>
+        <v>-15.73920272960252</v>
       </c>
       <c r="D65">
-        <v>12.50969796764337</v>
+        <v>12.34719727039747</v>
       </c>
       <c r="E65">
-        <v>40.73129999999999</v>
+        <v>41.47639999999999</v>
       </c>
       <c r="F65">
-        <v>46.94129999999999</v>
+        <v>47.68639999999999</v>
       </c>
       <c r="G65">
         <v>19.6</v>
@@ -6617,37 +6617,37 @@
         <v>3.43</v>
       </c>
       <c r="M65">
-        <v>11.06875854</v>
+        <v>11.24445312</v>
       </c>
       <c r="N65">
-        <v>-7.638758539999998</v>
+        <v>-7.81445312</v>
       </c>
       <c r="O65">
-        <v>-1.145813781</v>
+        <v>-1.172167968</v>
       </c>
       <c r="P65">
-        <v>-6.492944758999998</v>
+        <v>-6.642285151999999</v>
       </c>
       <c r="Q65">
-        <v>-3.982944758999998</v>
+        <v>-4.132285152</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1311289826771138</v>
+        <v>0.1334992321959225</v>
       </c>
       <c r="T65">
-        <v>1.618659270375019</v>
+        <v>1.663622027885437</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04648217757580609</v>
+        <v>0.04575589355118411</v>
       </c>
       <c r="W65">
-        <v>0.2248395025276249</v>
+        <v>0.2250107603006308</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3098811838387072</v>
+        <v>0.3050392903412273</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1920666101829358</v>
+        <v>0.1939666101829358</v>
       </c>
       <c r="C66">
-        <v>-15.73920272960252</v>
+        <v>-16.64263580332805</v>
       </c>
       <c r="D66">
-        <v>12.34719727039747</v>
+        <v>12.18886419667195</v>
       </c>
       <c r="E66">
-        <v>41.47639999999999</v>
+        <v>42.22149999999999</v>
       </c>
       <c r="F66">
-        <v>47.68639999999999</v>
+        <v>48.43149999999999</v>
       </c>
       <c r="G66">
         <v>19.6</v>
@@ -6699,37 +6699,37 @@
         <v>3.43</v>
       </c>
       <c r="M66">
-        <v>11.24445312</v>
+        <v>11.4201477</v>
       </c>
       <c r="N66">
-        <v>-7.81445312</v>
+        <v>-7.9901477</v>
       </c>
       <c r="O66">
-        <v>-1.172167968</v>
+        <v>-1.198522155</v>
       </c>
       <c r="P66">
-        <v>-6.642285151999999</v>
+        <v>-6.791625545</v>
       </c>
       <c r="Q66">
-        <v>-4.132285152</v>
+        <v>-4.281625544999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1334992321959225</v>
+        <v>0.1360049245443774</v>
       </c>
       <c r="T66">
-        <v>1.663622027885437</v>
+        <v>1.711154085825021</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04575589355118411</v>
+        <v>0.04505195672731974</v>
       </c>
       <c r="W66">
-        <v>0.2250107603006308</v>
+        <v>0.225176748603698</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3050392903412273</v>
+        <v>0.3003463781821316</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1939666101829358</v>
+        <v>0.1958666101829358</v>
       </c>
       <c r="C67">
-        <v>-16.64263580332805</v>
+        <v>-17.54205955293127</v>
       </c>
       <c r="D67">
-        <v>12.18886419667195</v>
+        <v>12.03454044706872</v>
       </c>
       <c r="E67">
-        <v>42.22149999999999</v>
+        <v>42.96659999999999</v>
       </c>
       <c r="F67">
-        <v>48.43149999999999</v>
+        <v>49.17659999999999</v>
       </c>
       <c r="G67">
         <v>19.6</v>
@@ -6781,37 +6781,37 @@
         <v>3.43</v>
       </c>
       <c r="M67">
-        <v>11.4201477</v>
+        <v>11.59584228</v>
       </c>
       <c r="N67">
-        <v>-7.9901477</v>
+        <v>-8.16584228</v>
       </c>
       <c r="O67">
-        <v>-1.198522155</v>
+        <v>-1.224876342</v>
       </c>
       <c r="P67">
-        <v>-6.791625545</v>
+        <v>-6.940965938</v>
       </c>
       <c r="Q67">
-        <v>-4.281625544999999</v>
+        <v>-4.430965938</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1360049245443774</v>
+        <v>0.1386580105603885</v>
       </c>
       <c r="T67">
-        <v>1.711154085825021</v>
+        <v>1.761482147172815</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04505195672731974</v>
+        <v>0.04436935132236035</v>
       </c>
       <c r="W67">
-        <v>0.225176748603698</v>
+        <v>0.2253377069581874</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3003463781821316</v>
+        <v>0.2957956754824023</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1958666101829358</v>
+        <v>0.1977666101829358</v>
       </c>
       <c r="C68">
-        <v>-17.54205955293127</v>
+        <v>-18.43762436110134</v>
       </c>
       <c r="D68">
-        <v>12.03454044706872</v>
+        <v>11.88407563889865</v>
       </c>
       <c r="E68">
-        <v>42.96659999999999</v>
+        <v>43.71169999999999</v>
       </c>
       <c r="F68">
-        <v>49.17659999999999</v>
+        <v>49.92169999999999</v>
       </c>
       <c r="G68">
         <v>19.6</v>
@@ -6863,37 +6863,37 @@
         <v>3.43</v>
       </c>
       <c r="M68">
-        <v>11.59584228</v>
+        <v>11.77153686</v>
       </c>
       <c r="N68">
-        <v>-8.16584228</v>
+        <v>-8.34153686</v>
       </c>
       <c r="O68">
-        <v>-1.224876342</v>
+        <v>-1.251230529</v>
       </c>
       <c r="P68">
-        <v>-6.940965938</v>
+        <v>-7.090306331</v>
       </c>
       <c r="Q68">
-        <v>-4.430965938</v>
+        <v>-4.580306330999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1386580105603885</v>
+        <v>0.1414718896682791</v>
       </c>
       <c r="T68">
-        <v>1.761482147172815</v>
+        <v>1.81486039405684</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04436935132236035</v>
+        <v>0.04370712219814601</v>
       </c>
       <c r="W68">
-        <v>0.2253377069581874</v>
+        <v>0.2254938605856772</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2957956754824023</v>
+        <v>0.2913808146543068</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1977666101829358</v>
+        <v>0.1996666101829358</v>
       </c>
       <c r="C69">
-        <v>-18.43762436110134</v>
+        <v>-19.32947318261019</v>
       </c>
       <c r="D69">
-        <v>11.88407563889865</v>
+        <v>11.7373268173898</v>
       </c>
       <c r="E69">
-        <v>43.71169999999999</v>
+        <v>44.45679999999999</v>
       </c>
       <c r="F69">
-        <v>49.92169999999999</v>
+        <v>50.66679999999999</v>
       </c>
       <c r="G69">
         <v>19.6</v>
@@ -6945,37 +6945,37 @@
         <v>3.43</v>
       </c>
       <c r="M69">
-        <v>11.77153686</v>
+        <v>11.94723144</v>
       </c>
       <c r="N69">
-        <v>-8.34153686</v>
+        <v>-8.51723144</v>
       </c>
       <c r="O69">
-        <v>-1.251230529</v>
+        <v>-1.277584716</v>
       </c>
       <c r="P69">
-        <v>-7.090306331</v>
+        <v>-7.239646724</v>
       </c>
       <c r="Q69">
-        <v>-4.580306330999999</v>
+        <v>-4.729646724</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1414718896682791</v>
+        <v>0.1444616362204128</v>
       </c>
       <c r="T69">
-        <v>1.81486039405684</v>
+        <v>1.871574781371116</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04370712219814601</v>
+        <v>0.04306437040111446</v>
       </c>
       <c r="W69">
-        <v>0.2254938605856772</v>
+        <v>0.2256454214594172</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2913808146543068</v>
+        <v>0.2870958026740963</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1996666101829358</v>
+        <v>0.2015666101829358</v>
       </c>
       <c r="C70">
-        <v>-19.32947318261019</v>
+        <v>-20.21774199733146</v>
       </c>
       <c r="D70">
-        <v>11.7373268173898</v>
+        <v>11.59415800266853</v>
       </c>
       <c r="E70">
-        <v>44.45679999999999</v>
+        <v>45.20189999999999</v>
       </c>
       <c r="F70">
-        <v>50.66679999999999</v>
+        <v>51.4119</v>
       </c>
       <c r="G70">
         <v>19.6</v>
@@ -7027,37 +7027,37 @@
         <v>3.43</v>
       </c>
       <c r="M70">
-        <v>11.94723144</v>
+        <v>12.12292602</v>
       </c>
       <c r="N70">
-        <v>-8.51723144</v>
+        <v>-8.69292602</v>
       </c>
       <c r="O70">
-        <v>-1.277584716</v>
+        <v>-1.303938903</v>
       </c>
       <c r="P70">
-        <v>-7.239646724</v>
+        <v>-7.388987117</v>
       </c>
       <c r="Q70">
-        <v>-4.729646724</v>
+        <v>-4.878987116999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1444616362204128</v>
+        <v>0.1476442696468777</v>
       </c>
       <c r="T70">
-        <v>1.871574781371116</v>
+        <v>1.931948161415346</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04306437040111446</v>
+        <v>0.04244024909095338</v>
       </c>
       <c r="W70">
-        <v>0.2256454214594172</v>
+        <v>0.2257925892643532</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2870958026740963</v>
+        <v>0.2829349939396891</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2015666101829358</v>
+        <v>0.2034666101829358</v>
       </c>
       <c r="C71">
-        <v>-20.21774199733146</v>
+        <v>-21.10256023050405</v>
       </c>
       <c r="D71">
-        <v>11.59415800266853</v>
+        <v>11.45443976949595</v>
       </c>
       <c r="E71">
-        <v>45.20189999999999</v>
+        <v>45.947</v>
       </c>
       <c r="F71">
-        <v>51.4119</v>
+        <v>52.157</v>
       </c>
       <c r="G71">
         <v>19.6</v>
@@ -7109,37 +7109,37 @@
         <v>3.43</v>
       </c>
       <c r="M71">
-        <v>12.12292602</v>
+        <v>12.2986206</v>
       </c>
       <c r="N71">
-        <v>-8.69292602</v>
+        <v>-8.8686206</v>
       </c>
       <c r="O71">
-        <v>-1.303938903</v>
+        <v>-1.33029309</v>
       </c>
       <c r="P71">
-        <v>-7.388987117</v>
+        <v>-7.53832751</v>
       </c>
       <c r="Q71">
-        <v>-4.878987116999999</v>
+        <v>-5.02832751</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1476442696468777</v>
+        <v>0.151039078635107</v>
       </c>
       <c r="T71">
-        <v>1.931948161415346</v>
+        <v>1.996346433462524</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04244024909095338</v>
+        <v>0.04183395981822547</v>
       </c>
       <c r="W71">
-        <v>0.2257925892643532</v>
+        <v>0.2259355522748625</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2829349939396891</v>
+        <v>0.2788930654548365</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2034666101829358</v>
+        <v>0.2053666101829358</v>
       </c>
       <c r="C72">
-        <v>-21.10256023050405</v>
+        <v>-21.98405114297059</v>
       </c>
       <c r="D72">
-        <v>11.45443976949595</v>
+        <v>11.31804885702941</v>
       </c>
       <c r="E72">
-        <v>45.947</v>
+        <v>46.6921</v>
       </c>
       <c r="F72">
-        <v>52.157</v>
+        <v>52.9021</v>
       </c>
       <c r="G72">
         <v>19.6</v>
@@ -7191,37 +7191,37 @@
         <v>3.43</v>
       </c>
       <c r="M72">
-        <v>12.2986206</v>
+        <v>12.47431518</v>
       </c>
       <c r="N72">
-        <v>-8.8686206</v>
+        <v>-9.04431518</v>
       </c>
       <c r="O72">
-        <v>-1.33029309</v>
+        <v>-1.356647277</v>
       </c>
       <c r="P72">
-        <v>-7.53832751</v>
+        <v>-7.687667902999999</v>
       </c>
       <c r="Q72">
-        <v>-5.02832751</v>
+        <v>-5.177667903</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.151039078635107</v>
+        <v>0.1546680123811452</v>
       </c>
       <c r="T72">
-        <v>1.996346433462524</v>
+        <v>2.065185965650888</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04183395981822547</v>
+        <v>0.04124474911656032</v>
       </c>
       <c r="W72">
-        <v>0.2259355522748625</v>
+        <v>0.2260744881583151</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2788930654548365</v>
+        <v>0.2749649941104021</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2053666101829358</v>
+        <v>0.2072666101829358</v>
       </c>
       <c r="C73">
-        <v>-21.98405114297057</v>
+        <v>-22.86233219386396</v>
       </c>
       <c r="D73">
-        <v>11.31804885702942</v>
+        <v>11.18486780613603</v>
       </c>
       <c r="E73">
-        <v>46.69209999999999</v>
+        <v>47.43719999999999</v>
       </c>
       <c r="F73">
-        <v>52.90209999999999</v>
+        <v>53.64719999999999</v>
       </c>
       <c r="G73">
         <v>19.6</v>
@@ -7273,37 +7273,37 @@
         <v>3.43</v>
       </c>
       <c r="M73">
-        <v>12.47431518</v>
+        <v>12.65000976</v>
       </c>
       <c r="N73">
-        <v>-9.044315179999998</v>
+        <v>-9.220009759999998</v>
       </c>
       <c r="O73">
-        <v>-1.356647277</v>
+        <v>-1.383001464</v>
       </c>
       <c r="P73">
-        <v>-7.687667902999999</v>
+        <v>-7.837008295999999</v>
       </c>
       <c r="Q73">
-        <v>-5.177667902999998</v>
+        <v>-5.327008295999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1546680123811452</v>
+        <v>0.1585561556804718</v>
       </c>
       <c r="T73">
-        <v>2.065185965650887</v>
+        <v>2.138942607281276</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04124474911656033</v>
+        <v>0.04067190537883032</v>
       </c>
       <c r="W73">
-        <v>0.2260744881583151</v>
+        <v>0.2262095647116718</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2749649941104022</v>
+        <v>0.2711460358588688</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2072666101829358</v>
+        <v>0.2091666101829358</v>
       </c>
       <c r="C74">
-        <v>-22.86233219386396</v>
+        <v>-23.73751537798501</v>
       </c>
       <c r="D74">
-        <v>11.18486780613603</v>
+        <v>11.05478462201498</v>
       </c>
       <c r="E74">
-        <v>47.43719999999999</v>
+        <v>48.18229999999999</v>
       </c>
       <c r="F74">
-        <v>53.64719999999999</v>
+        <v>54.39229999999999</v>
       </c>
       <c r="G74">
         <v>19.6</v>
@@ -7355,37 +7355,37 @@
         <v>3.43</v>
       </c>
       <c r="M74">
-        <v>12.65000976</v>
+        <v>12.82570434</v>
       </c>
       <c r="N74">
-        <v>-9.220009759999998</v>
+        <v>-9.395704339999998</v>
       </c>
       <c r="O74">
-        <v>-1.383001464</v>
+        <v>-1.409355651</v>
       </c>
       <c r="P74">
-        <v>-7.837008295999999</v>
+        <v>-7.986348688999999</v>
       </c>
       <c r="Q74">
-        <v>-5.327008295999999</v>
+        <v>-5.476348688999998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1585561556804718</v>
+        <v>0.1627323095945633</v>
       </c>
       <c r="T74">
-        <v>2.138942607281276</v>
+        <v>2.218162703847249</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04067190537883032</v>
+        <v>0.04011475599007922</v>
       </c>
       <c r="W74">
-        <v>0.2262095647116718</v>
+        <v>0.2263409405375393</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2711460358588688</v>
+        <v>0.2674317066005282</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2091666101829358</v>
+        <v>0.2110666101829358</v>
       </c>
       <c r="C75">
-        <v>-23.73751537798501</v>
+        <v>-24.60970753990796</v>
       </c>
       <c r="D75">
-        <v>11.05478462201498</v>
+        <v>10.92769246009203</v>
       </c>
       <c r="E75">
-        <v>48.18229999999999</v>
+        <v>48.92739999999999</v>
       </c>
       <c r="F75">
-        <v>54.39229999999999</v>
+        <v>55.13739999999999</v>
       </c>
       <c r="G75">
         <v>19.6</v>
@@ -7437,37 +7437,37 @@
         <v>3.43</v>
       </c>
       <c r="M75">
-        <v>12.82570434</v>
+        <v>13.00139892</v>
       </c>
       <c r="N75">
-        <v>-9.395704339999998</v>
+        <v>-9.571398919999998</v>
       </c>
       <c r="O75">
-        <v>-1.409355651</v>
+        <v>-1.435709838</v>
       </c>
       <c r="P75">
-        <v>-7.986348688999999</v>
+        <v>-8.135689081999999</v>
       </c>
       <c r="Q75">
-        <v>-5.476348688999998</v>
+        <v>-5.625689081999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1627323095945633</v>
+        <v>0.1672297061174311</v>
       </c>
       <c r="T75">
-        <v>2.218162703847249</v>
+        <v>2.30347665399522</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04011475599007922</v>
+        <v>0.03957266469291599</v>
       </c>
       <c r="W75">
-        <v>0.2263409405375393</v>
+        <v>0.2264687656654104</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2674317066005282</v>
+        <v>0.26381776461944</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2110666101829358</v>
+        <v>0.2129666101829358</v>
       </c>
       <c r="C76">
-        <v>-24.60970753990796</v>
+        <v>-25.47901066666549</v>
       </c>
       <c r="D76">
-        <v>10.92769246009203</v>
+        <v>10.80348933333451</v>
       </c>
       <c r="E76">
-        <v>48.92739999999999</v>
+        <v>49.67249999999999</v>
       </c>
       <c r="F76">
-        <v>55.13739999999999</v>
+        <v>55.88249999999999</v>
       </c>
       <c r="G76">
         <v>19.6</v>
@@ -7519,37 +7519,37 @@
         <v>3.43</v>
       </c>
       <c r="M76">
-        <v>13.00139892</v>
+        <v>13.1770935</v>
       </c>
       <c r="N76">
-        <v>-9.571398919999998</v>
+        <v>-9.7470935</v>
       </c>
       <c r="O76">
-        <v>-1.435709838</v>
+        <v>-1.462064025</v>
       </c>
       <c r="P76">
-        <v>-8.135689081999999</v>
+        <v>-8.285029475</v>
       </c>
       <c r="Q76">
-        <v>-5.625689081999999</v>
+        <v>-5.775029475</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1672297061174311</v>
+        <v>0.1720868943621284</v>
       </c>
       <c r="T76">
-        <v>2.30347665399522</v>
+        <v>2.395615720155029</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03957266469291599</v>
+        <v>0.0390450291636771</v>
       </c>
       <c r="W76">
-        <v>0.2264687656654104</v>
+        <v>0.226593182123205</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.26381776461944</v>
+        <v>0.260300194424514</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2129666101829358</v>
+        <v>0.2148666101829358</v>
       </c>
       <c r="C77">
-        <v>-25.47901066666549</v>
+        <v>-26.34552216069807</v>
       </c>
       <c r="D77">
-        <v>10.80348933333451</v>
+        <v>10.68207783930192</v>
       </c>
       <c r="E77">
-        <v>49.67249999999999</v>
+        <v>50.41759999999999</v>
       </c>
       <c r="F77">
-        <v>55.88249999999999</v>
+        <v>56.62759999999999</v>
       </c>
       <c r="G77">
         <v>19.6</v>
@@ -7601,37 +7601,37 @@
         <v>3.43</v>
       </c>
       <c r="M77">
-        <v>13.1770935</v>
+        <v>13.35278808</v>
       </c>
       <c r="N77">
-        <v>-9.7470935</v>
+        <v>-9.92278808</v>
       </c>
       <c r="O77">
-        <v>-1.462064025</v>
+        <v>-1.488418212</v>
       </c>
       <c r="P77">
-        <v>-8.285029475</v>
+        <v>-8.434369868000001</v>
       </c>
       <c r="Q77">
-        <v>-5.775029475</v>
+        <v>-5.924369868000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1720868943621284</v>
+        <v>0.1773488482938838</v>
       </c>
       <c r="T77">
-        <v>2.395615720155029</v>
+        <v>2.495433041828155</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0390450291636771</v>
+        <v>0.03853127877994451</v>
       </c>
       <c r="W77">
-        <v>0.226593182123205</v>
+        <v>0.2267143244636891</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.260300194424514</v>
+        <v>0.2568751918662967</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2148666101829358</v>
+        <v>0.2167666101829358</v>
       </c>
       <c r="C78">
-        <v>-26.34552216069807</v>
+        <v>-27.20933509460345</v>
       </c>
       <c r="D78">
-        <v>10.68207783930192</v>
+        <v>10.56336490539654</v>
       </c>
       <c r="E78">
-        <v>50.41759999999999</v>
+        <v>51.16269999999999</v>
       </c>
       <c r="F78">
-        <v>56.62759999999999</v>
+        <v>57.37269999999999</v>
       </c>
       <c r="G78">
         <v>19.6</v>
@@ -7683,37 +7683,37 @@
         <v>3.43</v>
       </c>
       <c r="M78">
-        <v>13.35278808</v>
+        <v>13.52848266</v>
       </c>
       <c r="N78">
-        <v>-9.92278808</v>
+        <v>-10.09848266</v>
       </c>
       <c r="O78">
-        <v>-1.488418212</v>
+        <v>-1.514772399</v>
       </c>
       <c r="P78">
-        <v>-8.434369868000001</v>
+        <v>-8.583710261</v>
       </c>
       <c r="Q78">
-        <v>-5.924369868000001</v>
+        <v>-6.073710261</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1773488482938838</v>
+        <v>0.1830683634370961</v>
       </c>
       <c r="T78">
-        <v>2.495433041828155</v>
+        <v>2.603930130603292</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03853127877994451</v>
+        <v>0.03803087256202315</v>
       </c>
       <c r="W78">
-        <v>0.2267143244636891</v>
+        <v>0.2268323202498749</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2568751918662967</v>
+        <v>0.2535391504134876</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2167666101829358</v>
+        <v>0.2186666101829358</v>
       </c>
       <c r="C79">
-        <v>-27.20933509460345</v>
+        <v>-28.07053844908592</v>
       </c>
       <c r="D79">
-        <v>10.56336490539654</v>
+        <v>10.44726155091407</v>
       </c>
       <c r="E79">
-        <v>51.16269999999999</v>
+        <v>51.90779999999999</v>
       </c>
       <c r="F79">
-        <v>57.37269999999999</v>
+        <v>58.1178</v>
       </c>
       <c r="G79">
         <v>19.6</v>
@@ -7765,37 +7765,37 @@
         <v>3.43</v>
       </c>
       <c r="M79">
-        <v>13.52848266</v>
+        <v>13.70417724</v>
       </c>
       <c r="N79">
-        <v>-10.09848266</v>
+        <v>-10.27417724</v>
       </c>
       <c r="O79">
-        <v>-1.514772399</v>
+        <v>-1.541126586</v>
       </c>
       <c r="P79">
-        <v>-8.583710261</v>
+        <v>-8.733050653999999</v>
       </c>
       <c r="Q79">
-        <v>-6.073710261</v>
+        <v>-6.223050654</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1830683634370961</v>
+        <v>0.1893078345024186</v>
       </c>
       <c r="T79">
-        <v>2.603930130603292</v>
+        <v>2.72229059108526</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03803087256202315</v>
+        <v>0.03754329727276645</v>
       </c>
       <c r="W79">
-        <v>0.2268323202498749</v>
+        <v>0.2269472905030817</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2535391504134876</v>
+        <v>0.2502886484851096</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2186666101829358</v>
+        <v>0.2205666101829358</v>
       </c>
       <c r="C80">
-        <v>-28.07053844908592</v>
+        <v>-28.9292173353844</v>
       </c>
       <c r="D80">
-        <v>10.44726155091407</v>
+        <v>10.33368266461559</v>
       </c>
       <c r="E80">
-        <v>51.90779999999999</v>
+        <v>52.6529</v>
       </c>
       <c r="F80">
-        <v>58.1178</v>
+        <v>58.8629</v>
       </c>
       <c r="G80">
         <v>19.6</v>
@@ -7847,37 +7847,37 @@
         <v>3.43</v>
       </c>
       <c r="M80">
-        <v>13.70417724</v>
+        <v>13.87987182</v>
       </c>
       <c r="N80">
-        <v>-10.27417724</v>
+        <v>-10.44987182</v>
       </c>
       <c r="O80">
-        <v>-1.541126586</v>
+        <v>-1.567480773</v>
       </c>
       <c r="P80">
-        <v>-8.733050653999999</v>
+        <v>-8.882391047</v>
       </c>
       <c r="Q80">
-        <v>-6.223050654</v>
+        <v>-6.372391047000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1893078345024186</v>
+        <v>0.1961415409072957</v>
       </c>
       <c r="T80">
-        <v>2.72229059108526</v>
+        <v>2.851923476375035</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03754329727276645</v>
+        <v>0.03706806566171877</v>
       </c>
       <c r="W80">
-        <v>0.2269472905030817</v>
+        <v>0.2270593501169667</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2502886484851096</v>
+        <v>0.2471204377447918</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2205666101829358</v>
+        <v>0.2224666101829358</v>
       </c>
       <c r="C81">
-        <v>-28.9292173353844</v>
+        <v>-29.78545320334744</v>
       </c>
       <c r="D81">
-        <v>10.33368266461559</v>
+        <v>10.22254679665256</v>
       </c>
       <c r="E81">
-        <v>52.6529</v>
+        <v>53.398</v>
       </c>
       <c r="F81">
-        <v>58.8629</v>
+        <v>59.608</v>
       </c>
       <c r="G81">
         <v>19.6</v>
@@ -7929,37 +7929,37 @@
         <v>3.43</v>
       </c>
       <c r="M81">
-        <v>13.87987182</v>
+        <v>14.0555664</v>
       </c>
       <c r="N81">
-        <v>-10.44987182</v>
+        <v>-10.6255664</v>
       </c>
       <c r="O81">
-        <v>-1.567480773</v>
+        <v>-1.59383496</v>
       </c>
       <c r="P81">
-        <v>-8.882391047</v>
+        <v>-9.03173144</v>
       </c>
       <c r="Q81">
-        <v>-6.372391047000001</v>
+        <v>-6.52173144</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1961415409072957</v>
+        <v>0.2036586179526605</v>
       </c>
       <c r="T81">
-        <v>2.851923476375035</v>
+        <v>2.994519650193787</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03706806566171877</v>
+        <v>0.03660471484094729</v>
       </c>
       <c r="W81">
-        <v>0.2270593501169667</v>
+        <v>0.2271686082405046</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2471204377447918</v>
+        <v>0.2440314322729819</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2224666101829358</v>
+        <v>0.2243666101829358</v>
       </c>
       <c r="C82">
-        <v>-29.78545320334744</v>
+        <v>-30.63932403622456</v>
       </c>
       <c r="D82">
-        <v>10.22254679665256</v>
+        <v>10.11377596377544</v>
       </c>
       <c r="E82">
-        <v>53.398</v>
+        <v>54.1431</v>
       </c>
       <c r="F82">
-        <v>59.608</v>
+        <v>60.3531</v>
       </c>
       <c r="G82">
         <v>19.6</v>
@@ -8011,37 +8011,37 @@
         <v>3.43</v>
       </c>
       <c r="M82">
-        <v>14.0555664</v>
+        <v>14.23126098</v>
       </c>
       <c r="N82">
-        <v>-10.6255664</v>
+        <v>-10.80126098</v>
       </c>
       <c r="O82">
-        <v>-1.59383496</v>
+        <v>-1.620189147</v>
       </c>
       <c r="P82">
-        <v>-9.03173144</v>
+        <v>-9.181071833000001</v>
       </c>
       <c r="Q82">
-        <v>-6.52173144</v>
+        <v>-6.671071833000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2036586179526605</v>
+        <v>0.2119669662659584</v>
       </c>
       <c r="T82">
-        <v>2.994519650193787</v>
+        <v>3.152125947572407</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03660471484094729</v>
+        <v>0.0361528047811825</v>
       </c>
       <c r="W82">
-        <v>0.2271686082405046</v>
+        <v>0.2272751686325972</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2440314322729819</v>
+        <v>0.2410186985412167</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2243666101829358</v>
+        <v>0.2262666101829358</v>
       </c>
       <c r="C83">
-        <v>-30.63932403622456</v>
+        <v>-31.49090453315247</v>
       </c>
       <c r="D83">
-        <v>10.11377596377544</v>
+        <v>10.00729546684753</v>
       </c>
       <c r="E83">
-        <v>54.1431</v>
+        <v>54.8882</v>
       </c>
       <c r="F83">
-        <v>60.3531</v>
+        <v>61.0982</v>
       </c>
       <c r="G83">
         <v>19.6</v>
@@ -8093,37 +8093,37 @@
         <v>3.43</v>
       </c>
       <c r="M83">
-        <v>14.23126098</v>
+        <v>14.40695556</v>
       </c>
       <c r="N83">
-        <v>-10.80126098</v>
+        <v>-10.97695556</v>
       </c>
       <c r="O83">
-        <v>-1.620189147</v>
+        <v>-1.646543334</v>
       </c>
       <c r="P83">
-        <v>-9.181071833000001</v>
+        <v>-9.330412226</v>
       </c>
       <c r="Q83">
-        <v>-6.671071833000001</v>
+        <v>-6.820412226</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2119669662659584</v>
+        <v>0.221198464391845</v>
       </c>
       <c r="T83">
-        <v>3.152125947572407</v>
+        <v>3.327244055770874</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0361528047811825</v>
+        <v>0.03571191691799736</v>
       </c>
       <c r="W83">
-        <v>0.2272751686325972</v>
+        <v>0.2273791299907362</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2410186985412167</v>
+        <v>0.2380794461199823</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2262666101829358</v>
+        <v>0.2281666101829358</v>
       </c>
       <c r="C84">
-        <v>-31.49090453315247</v>
+        <v>-32.340266280234</v>
       </c>
       <c r="D84">
-        <v>10.00729546684753</v>
+        <v>9.903033719765995</v>
       </c>
       <c r="E84">
-        <v>54.8882</v>
+        <v>55.6333</v>
       </c>
       <c r="F84">
-        <v>61.0982</v>
+        <v>61.8433</v>
       </c>
       <c r="G84">
         <v>19.6</v>
@@ -8175,37 +8175,37 @@
         <v>3.43</v>
       </c>
       <c r="M84">
-        <v>14.40695556</v>
+        <v>14.58265014</v>
       </c>
       <c r="N84">
-        <v>-10.97695556</v>
+        <v>-11.15265014</v>
       </c>
       <c r="O84">
-        <v>-1.646543334</v>
+        <v>-1.672897521</v>
       </c>
       <c r="P84">
-        <v>-9.330412226</v>
+        <v>-9.479752619000001</v>
       </c>
       <c r="Q84">
-        <v>-6.820412226</v>
+        <v>-6.969752619000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.221198464391845</v>
+        <v>0.2315160211207771</v>
       </c>
       <c r="T84">
-        <v>3.327244055770874</v>
+        <v>3.522964294345632</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03571191691799736</v>
+        <v>0.03528165285874437</v>
       </c>
       <c r="W84">
-        <v>0.2273791299907362</v>
+        <v>0.2274805862559081</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2380794461199823</v>
+        <v>0.2352110190582958</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2281666101829358</v>
+        <v>0.2300666101829358</v>
       </c>
       <c r="C85">
-        <v>-32.340266280234</v>
+        <v>-33.18747791103284</v>
       </c>
       <c r="D85">
-        <v>9.903033719765995</v>
+        <v>9.800922088967154</v>
       </c>
       <c r="E85">
-        <v>55.6333</v>
+        <v>56.3784</v>
       </c>
       <c r="F85">
-        <v>61.8433</v>
+        <v>62.5884</v>
       </c>
       <c r="G85">
         <v>19.6</v>
@@ -8257,37 +8257,37 @@
         <v>3.43</v>
       </c>
       <c r="M85">
-        <v>14.58265014</v>
+        <v>14.75834472</v>
       </c>
       <c r="N85">
-        <v>-11.15265014</v>
+        <v>-11.32834472</v>
       </c>
       <c r="O85">
-        <v>-1.672897521</v>
+        <v>-1.699251708</v>
       </c>
       <c r="P85">
-        <v>-9.479752619000001</v>
+        <v>-9.629093012</v>
       </c>
       <c r="Q85">
-        <v>-6.969752619000001</v>
+        <v>-7.119093012</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2315160211207771</v>
+        <v>0.2431232724408257</v>
       </c>
       <c r="T85">
-        <v>3.522964294345632</v>
+        <v>3.743149562742234</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03528165285874437</v>
+        <v>0.03486163318185456</v>
       </c>
       <c r="W85">
-        <v>0.2274805862559081</v>
+        <v>0.2275796268957187</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2352110190582958</v>
+        <v>0.2324108878790303</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2300666101829358</v>
+        <v>0.2319666101829358</v>
       </c>
       <c r="C86">
-        <v>-33.18747791103284</v>
+        <v>-34.03260525724031</v>
       </c>
       <c r="D86">
-        <v>9.800922088967148</v>
+        <v>9.700894742759688</v>
       </c>
       <c r="E86">
-        <v>56.37839999999999</v>
+        <v>57.12349999999999</v>
       </c>
       <c r="F86">
-        <v>62.58839999999999</v>
+        <v>63.33349999999999</v>
       </c>
       <c r="G86">
         <v>19.6</v>
@@ -8339,37 +8339,37 @@
         <v>3.43</v>
       </c>
       <c r="M86">
-        <v>14.75834472</v>
+        <v>14.9340393</v>
       </c>
       <c r="N86">
-        <v>-11.32834472</v>
+        <v>-11.5040393</v>
       </c>
       <c r="O86">
-        <v>-1.699251708</v>
+        <v>-1.725605895</v>
       </c>
       <c r="P86">
-        <v>-9.629093011999998</v>
+        <v>-9.778433404999999</v>
       </c>
       <c r="Q86">
-        <v>-7.119093011999999</v>
+        <v>-7.268433405</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2431232724408256</v>
+        <v>0.2562781572702139</v>
       </c>
       <c r="T86">
-        <v>3.743149562742232</v>
+        <v>3.992692866925048</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03486163318185456</v>
+        <v>0.03445149632089156</v>
       </c>
       <c r="W86">
-        <v>0.2275796268957187</v>
+        <v>0.2276763371675338</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2324108878790304</v>
+        <v>0.2296766421392771</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2319666101829358</v>
+        <v>0.2338666101829358</v>
       </c>
       <c r="C87">
-        <v>-34.03260525724031</v>
+        <v>-34.87571149020911</v>
       </c>
       <c r="D87">
-        <v>9.700894742759688</v>
+        <v>9.602888509790885</v>
       </c>
       <c r="E87">
-        <v>57.12349999999999</v>
+        <v>57.86859999999999</v>
       </c>
       <c r="F87">
-        <v>63.33349999999999</v>
+        <v>64.07859999999999</v>
       </c>
       <c r="G87">
         <v>19.6</v>
@@ -8421,37 +8421,37 @@
         <v>3.43</v>
       </c>
       <c r="M87">
-        <v>14.9340393</v>
+        <v>15.10973388</v>
       </c>
       <c r="N87">
-        <v>-11.5040393</v>
+        <v>-11.67973388</v>
       </c>
       <c r="O87">
-        <v>-1.725605895</v>
+        <v>-1.751960082</v>
       </c>
       <c r="P87">
-        <v>-9.778433404999999</v>
+        <v>-9.927773797999999</v>
       </c>
       <c r="Q87">
-        <v>-7.268433405</v>
+        <v>-7.417773797999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2562781572702139</v>
+        <v>0.2713123113609435</v>
       </c>
       <c r="T87">
-        <v>3.992692866925048</v>
+        <v>4.277885214562551</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03445149632089156</v>
+        <v>0.03405089752646259</v>
       </c>
       <c r="W87">
-        <v>0.2276763371675338</v>
+        <v>0.2277707983632601</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2296766421392771</v>
+        <v>0.2270059835097507</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2338666101829358</v>
+        <v>0.2357666101829358</v>
       </c>
       <c r="C88">
-        <v>-34.87571149020911</v>
+        <v>-35.71685725399377</v>
       </c>
       <c r="D88">
-        <v>9.602888509790885</v>
+        <v>9.506842746006217</v>
       </c>
       <c r="E88">
-        <v>57.86859999999999</v>
+        <v>58.61369999999999</v>
       </c>
       <c r="F88">
-        <v>64.07859999999999</v>
+        <v>64.82369999999999</v>
       </c>
       <c r="G88">
         <v>19.6</v>
@@ -8503,37 +8503,37 @@
         <v>3.43</v>
       </c>
       <c r="M88">
-        <v>15.10973388</v>
+        <v>15.28542846</v>
       </c>
       <c r="N88">
-        <v>-11.67973388</v>
+        <v>-11.85542846</v>
       </c>
       <c r="O88">
-        <v>-1.751960082</v>
+        <v>-1.778314269</v>
       </c>
       <c r="P88">
-        <v>-9.927773797999999</v>
+        <v>-10.077114191</v>
       </c>
       <c r="Q88">
-        <v>-7.417773797999999</v>
+        <v>-7.567114191</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2713123113609435</v>
+        <v>0.2886594122348622</v>
       </c>
       <c r="T88">
-        <v>4.277885214562551</v>
+        <v>4.606953307990439</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03405089752646259</v>
+        <v>0.03365950789972164</v>
       </c>
       <c r="W88">
-        <v>0.2277707983632601</v>
+        <v>0.2278630880372456</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2270059835097507</v>
+        <v>0.2243967193314776</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2357666101829358</v>
+        <v>0.2376666101829358</v>
       </c>
       <c r="C89">
-        <v>-35.71685725399377</v>
+        <v>-36.55610079048607</v>
       </c>
       <c r="D89">
-        <v>9.506842746006217</v>
+        <v>9.412699209513921</v>
       </c>
       <c r="E89">
-        <v>58.61369999999999</v>
+        <v>59.3588</v>
       </c>
       <c r="F89">
-        <v>64.82369999999999</v>
+        <v>65.5688</v>
       </c>
       <c r="G89">
         <v>19.6</v>
@@ -8585,37 +8585,37 @@
         <v>3.43</v>
       </c>
       <c r="M89">
-        <v>15.28542846</v>
+        <v>15.46112304</v>
       </c>
       <c r="N89">
-        <v>-11.85542846</v>
+        <v>-12.03112304</v>
       </c>
       <c r="O89">
-        <v>-1.778314269</v>
+        <v>-1.804668456</v>
       </c>
       <c r="P89">
-        <v>-10.077114191</v>
+        <v>-10.226454584</v>
       </c>
       <c r="Q89">
-        <v>-7.567114191</v>
+        <v>-7.716454584000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2886594122348622</v>
+        <v>0.3088976965877675</v>
       </c>
       <c r="T89">
-        <v>4.606953307990439</v>
+        <v>4.990866083656311</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03365950789972164</v>
+        <v>0.03327701349177026</v>
       </c>
       <c r="W89">
-        <v>0.2278630880372456</v>
+        <v>0.2279532802186406</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2243967193314776</v>
+        <v>0.2218467566118018</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2376666101829358</v>
+        <v>0.2395666101829358</v>
       </c>
       <c r="C90">
-        <v>-36.55610079048607</v>
+        <v>-37.39349805718848</v>
       </c>
       <c r="D90">
-        <v>9.412699209513921</v>
+        <v>9.320401942811506</v>
       </c>
       <c r="E90">
-        <v>59.3588</v>
+        <v>60.10389999999999</v>
       </c>
       <c r="F90">
-        <v>65.5688</v>
+        <v>66.31389999999999</v>
       </c>
       <c r="G90">
         <v>19.6</v>
@@ -8667,37 +8667,37 @@
         <v>3.43</v>
       </c>
       <c r="M90">
-        <v>15.46112304</v>
+        <v>15.63681762</v>
       </c>
       <c r="N90">
-        <v>-12.03112304</v>
+        <v>-12.20681762</v>
       </c>
       <c r="O90">
-        <v>-1.804668456</v>
+        <v>-1.831022643</v>
       </c>
       <c r="P90">
-        <v>-10.226454584</v>
+        <v>-10.375794977</v>
       </c>
       <c r="Q90">
-        <v>-7.716454584000001</v>
+        <v>-7.865794976999998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3088976965877675</v>
+        <v>0.3328156690048373</v>
       </c>
       <c r="T90">
-        <v>4.990866083656311</v>
+        <v>5.444581182170521</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03327701349177026</v>
+        <v>0.03290311446377284</v>
       </c>
       <c r="W90">
-        <v>0.2279532802186406</v>
+        <v>0.2280414456094424</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2218467566118018</v>
+        <v>0.2193540964251522</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2395666101829358</v>
+        <v>0.2414666101829358</v>
       </c>
       <c r="C91">
-        <v>-37.39349805718848</v>
+        <v>-38.22910283812574</v>
       </c>
       <c r="D91">
-        <v>9.320401942811506</v>
+        <v>9.229897161874257</v>
       </c>
       <c r="E91">
-        <v>60.10389999999999</v>
+        <v>60.849</v>
       </c>
       <c r="F91">
-        <v>66.31389999999999</v>
+        <v>67.059</v>
       </c>
       <c r="G91">
         <v>19.6</v>
@@ -8749,37 +8749,37 @@
         <v>3.43</v>
       </c>
       <c r="M91">
-        <v>15.63681762</v>
+        <v>15.8125122</v>
       </c>
       <c r="N91">
-        <v>-12.20681762</v>
+        <v>-12.3825122</v>
       </c>
       <c r="O91">
-        <v>-1.831022643</v>
+        <v>-1.85737683</v>
       </c>
       <c r="P91">
-        <v>-10.375794977</v>
+        <v>-10.52513537</v>
       </c>
       <c r="Q91">
-        <v>-7.865794976999998</v>
+        <v>-8.015135370000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3328156690048373</v>
+        <v>0.361517235905321</v>
       </c>
       <c r="T91">
-        <v>5.444581182170521</v>
+        <v>5.989039300387573</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03290311446377284</v>
+        <v>0.03253752430306425</v>
       </c>
       <c r="W91">
-        <v>0.2280414456094424</v>
+        <v>0.2281276517693375</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2193540964251522</v>
+        <v>0.2169168286870949</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2414666101829358</v>
+        <v>0.2433666101829358</v>
       </c>
       <c r="C92">
-        <v>-38.22910283812574</v>
+        <v>-39.06296684835664</v>
       </c>
       <c r="D92">
-        <v>9.229897161874257</v>
+        <v>9.141133151643356</v>
       </c>
       <c r="E92">
-        <v>60.849</v>
+        <v>61.59409999999999</v>
       </c>
       <c r="F92">
-        <v>67.059</v>
+        <v>67.80409999999999</v>
       </c>
       <c r="G92">
         <v>19.6</v>
@@ -8831,37 +8831,37 @@
         <v>3.43</v>
       </c>
       <c r="M92">
-        <v>15.8125122</v>
+        <v>15.98820678</v>
       </c>
       <c r="N92">
-        <v>-12.3825122</v>
+        <v>-12.55820678</v>
       </c>
       <c r="O92">
-        <v>-1.85737683</v>
+        <v>-1.883731017</v>
       </c>
       <c r="P92">
-        <v>-10.52513537</v>
+        <v>-10.674475763</v>
       </c>
       <c r="Q92">
-        <v>-8.015135370000001</v>
+        <v>-8.164475763</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.361517235905321</v>
+        <v>0.3965969287836901</v>
       </c>
       <c r="T92">
-        <v>5.989039300387573</v>
+        <v>6.654488111541749</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03253752430306425</v>
+        <v>0.03217996909094267</v>
       </c>
       <c r="W92">
-        <v>0.2281276517693375</v>
+        <v>0.2282119632883557</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2169168286870949</v>
+        <v>0.2145331272729512</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2433666101829358</v>
+        <v>0.2452666101829358</v>
       </c>
       <c r="C93">
-        <v>-39.06296684835664</v>
+        <v>-39.8951398325127</v>
       </c>
       <c r="D93">
-        <v>9.141133151643356</v>
+        <v>9.0540601674873</v>
       </c>
       <c r="E93">
-        <v>61.59409999999999</v>
+        <v>62.3392</v>
       </c>
       <c r="F93">
-        <v>67.80409999999999</v>
+        <v>68.5492</v>
       </c>
       <c r="G93">
         <v>19.6</v>
@@ -8913,37 +8913,37 @@
         <v>3.43</v>
       </c>
       <c r="M93">
-        <v>15.98820678</v>
+        <v>16.16390136</v>
       </c>
       <c r="N93">
-        <v>-12.55820678</v>
+        <v>-12.73390136</v>
       </c>
       <c r="O93">
-        <v>-1.883731017</v>
+        <v>-1.910085204</v>
       </c>
       <c r="P93">
-        <v>-10.674475763</v>
+        <v>-10.823816156</v>
       </c>
       <c r="Q93">
-        <v>-8.164475763</v>
+        <v>-8.313816156000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3965969287836901</v>
+        <v>0.4404465448816514</v>
       </c>
       <c r="T93">
-        <v>6.654488111541749</v>
+        <v>7.486299125484469</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03217996909094267</v>
+        <v>0.03183018681821503</v>
       </c>
       <c r="W93">
-        <v>0.2282119632883557</v>
+        <v>0.2282944419482649</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2145331272729512</v>
+        <v>0.2122012454547668</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2452666101829358</v>
+        <v>0.2471666101829358</v>
       </c>
       <c r="C94">
-        <v>-39.8951398325127</v>
+        <v>-40.72566965775828</v>
       </c>
       <c r="D94">
-        <v>9.0540601674873</v>
+        <v>8.968630342241708</v>
       </c>
       <c r="E94">
-        <v>62.3392</v>
+        <v>63.08429999999999</v>
       </c>
       <c r="F94">
-        <v>68.5492</v>
+        <v>69.29429999999999</v>
       </c>
       <c r="G94">
         <v>19.6</v>
@@ -8995,37 +8995,37 @@
         <v>3.43</v>
       </c>
       <c r="M94">
-        <v>16.16390136</v>
+        <v>16.33959594</v>
       </c>
       <c r="N94">
-        <v>-12.73390136</v>
+        <v>-12.90959594</v>
       </c>
       <c r="O94">
-        <v>-1.910085204</v>
+        <v>-1.936439391</v>
       </c>
       <c r="P94">
-        <v>-10.823816156</v>
+        <v>-10.973156549</v>
       </c>
       <c r="Q94">
-        <v>-8.313816156000001</v>
+        <v>-8.463156548999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4404465448816514</v>
+        <v>0.4968246227218873</v>
       </c>
       <c r="T94">
-        <v>7.486299125484469</v>
+        <v>8.555770429125108</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03183018681821503</v>
+        <v>0.0314879267449009</v>
       </c>
       <c r="W94">
-        <v>0.2282944419482649</v>
+        <v>0.2283751468735524</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2122012454547668</v>
+        <v>0.2099195116326726</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2471666101829358</v>
+        <v>0.2490666101829358</v>
       </c>
       <c r="C95">
-        <v>-40.72566965775828</v>
+        <v>-41.55460240153714</v>
       </c>
       <c r="D95">
-        <v>8.968630342241708</v>
+        <v>8.88479759846286</v>
       </c>
       <c r="E95">
-        <v>63.08429999999999</v>
+        <v>63.8294</v>
       </c>
       <c r="F95">
-        <v>69.29429999999999</v>
+        <v>70.0394</v>
       </c>
       <c r="G95">
         <v>19.6</v>
@@ -9077,37 +9077,37 @@
         <v>3.43</v>
       </c>
       <c r="M95">
-        <v>16.33959594</v>
+        <v>16.51529052</v>
       </c>
       <c r="N95">
-        <v>-12.90959594</v>
+        <v>-13.08529052</v>
       </c>
       <c r="O95">
-        <v>-1.936439391</v>
+        <v>-1.962793578</v>
       </c>
       <c r="P95">
-        <v>-10.973156549</v>
+        <v>-11.122496942</v>
       </c>
       <c r="Q95">
-        <v>-8.463156548999999</v>
+        <v>-8.612496942000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4968246227218873</v>
+        <v>0.5719953931755354</v>
       </c>
       <c r="T95">
-        <v>8.555770429125108</v>
+        <v>9.98173216731263</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0314879267449009</v>
+        <v>0.0311529488008062</v>
       </c>
       <c r="W95">
-        <v>0.2283751468735524</v>
+        <v>0.2284541346727699</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2099195116326726</v>
+        <v>0.207686325338708</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2490666101829358</v>
+        <v>0.2509666101829358</v>
       </c>
       <c r="C96">
-        <v>-41.55460240153714</v>
+        <v>-42.38198243444321</v>
       </c>
       <c r="D96">
-        <v>8.88479759846286</v>
+        <v>8.802517565556785</v>
       </c>
       <c r="E96">
-        <v>63.8294</v>
+        <v>64.5745</v>
       </c>
       <c r="F96">
-        <v>70.0394</v>
+        <v>70.78449999999999</v>
       </c>
       <c r="G96">
         <v>19.6</v>
@@ -9159,37 +9159,37 @@
         <v>3.43</v>
       </c>
       <c r="M96">
-        <v>16.51529052</v>
+        <v>16.6909851</v>
       </c>
       <c r="N96">
-        <v>-13.08529052</v>
+        <v>-13.2609851</v>
       </c>
       <c r="O96">
-        <v>-1.962793578</v>
+        <v>-1.989147765</v>
       </c>
       <c r="P96">
-        <v>-11.122496942</v>
+        <v>-11.271837335</v>
       </c>
       <c r="Q96">
-        <v>-8.612496942000002</v>
+        <v>-8.761837334999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5719953931755354</v>
+        <v>0.6772344718106427</v>
       </c>
       <c r="T96">
-        <v>9.98173216731263</v>
+        <v>11.97807860077516</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0311529488008062</v>
+        <v>0.03082502302395561</v>
       </c>
       <c r="W96">
-        <v>0.2284541346727699</v>
+        <v>0.2285314595709513</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.207686325338708</v>
+        <v>0.2055001534930374</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2509666101829358</v>
+        <v>0.2528666101829358</v>
       </c>
       <c r="C97">
-        <v>-42.38198243444321</v>
+        <v>-43.20785249852927</v>
       </c>
       <c r="D97">
-        <v>8.802517565556785</v>
+        <v>8.721747501470729</v>
       </c>
       <c r="E97">
-        <v>64.5745</v>
+        <v>65.31960000000001</v>
       </c>
       <c r="F97">
-        <v>70.78449999999999</v>
+        <v>71.5296</v>
       </c>
       <c r="G97">
         <v>19.6</v>
@@ -9241,37 +9241,37 @@
         <v>3.43</v>
       </c>
       <c r="M97">
-        <v>16.6909851</v>
+        <v>16.86667968</v>
       </c>
       <c r="N97">
-        <v>-13.2609851</v>
+        <v>-13.43667968</v>
       </c>
       <c r="O97">
-        <v>-1.989147765</v>
+        <v>-2.015501952</v>
       </c>
       <c r="P97">
-        <v>-11.271837335</v>
+        <v>-11.421177728</v>
       </c>
       <c r="Q97">
-        <v>-8.761837334999999</v>
+        <v>-8.911177728</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6772344718106427</v>
+        <v>0.8350930897633038</v>
       </c>
       <c r="T97">
-        <v>11.97807860077516</v>
+        <v>14.97259825096896</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03082502302395561</v>
+        <v>0.03050392903412273</v>
       </c>
       <c r="W97">
-        <v>0.2285314595709513</v>
+        <v>0.2286071735337539</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2055001534930374</v>
+        <v>0.2033595268941516</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2528666101829358</v>
+        <v>0.2547666101829358</v>
       </c>
       <c r="C98">
-        <v>-43.20785249852926</v>
+        <v>-44.03225378134324</v>
       </c>
       <c r="D98">
-        <v>8.721747501470729</v>
+        <v>8.64244621865676</v>
       </c>
       <c r="E98">
-        <v>65.31959999999999</v>
+        <v>66.0647</v>
       </c>
       <c r="F98">
-        <v>71.52959999999999</v>
+        <v>72.2747</v>
       </c>
       <c r="G98">
         <v>19.6</v>
@@ -9323,37 +9323,37 @@
         <v>3.43</v>
       </c>
       <c r="M98">
-        <v>16.86667968</v>
+        <v>17.04237426</v>
       </c>
       <c r="N98">
-        <v>-13.43667968</v>
+        <v>-13.61237426</v>
       </c>
       <c r="O98">
-        <v>-2.015501952</v>
+        <v>-2.041856139</v>
       </c>
       <c r="P98">
-        <v>-11.421177728</v>
+        <v>-11.570518121</v>
       </c>
       <c r="Q98">
-        <v>-8.911177727999998</v>
+        <v>-9.060518120999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8350930897633017</v>
+        <v>1.098190786351069</v>
       </c>
       <c r="T98">
-        <v>14.97259825096892</v>
+        <v>19.96346433462523</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03050392903412274</v>
+        <v>0.0301894555389256</v>
       </c>
       <c r="W98">
-        <v>0.2286071735337539</v>
+        <v>0.2286813263839214</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2033595268941516</v>
+        <v>0.2012630369261706</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2547666101829358</v>
+        <v>0.2566666101829358</v>
       </c>
       <c r="C99">
-        <v>-44.03225378134324</v>
+        <v>-44.85522598596208</v>
       </c>
       <c r="D99">
-        <v>8.64244621865676</v>
+        <v>8.564574014037913</v>
       </c>
       <c r="E99">
-        <v>66.0647</v>
+        <v>66.8098</v>
       </c>
       <c r="F99">
-        <v>72.2747</v>
+        <v>73.01979999999999</v>
       </c>
       <c r="G99">
         <v>19.6</v>
@@ -9405,37 +9405,37 @@
         <v>3.43</v>
       </c>
       <c r="M99">
-        <v>17.04237426</v>
+        <v>17.21806884</v>
       </c>
       <c r="N99">
-        <v>-13.61237426</v>
+        <v>-13.78806884</v>
       </c>
       <c r="O99">
-        <v>-2.041856139</v>
+        <v>-2.068210326</v>
       </c>
       <c r="P99">
-        <v>-11.570518121</v>
+        <v>-11.719858514</v>
       </c>
       <c r="Q99">
-        <v>-9.060518120999999</v>
+        <v>-9.209858513999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.098190786351069</v>
+        <v>1.624386179526603</v>
       </c>
       <c r="T99">
-        <v>19.96346433462523</v>
+        <v>29.94519650193783</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0301894555389256</v>
+        <v>0.02988139987016105</v>
       </c>
       <c r="W99">
-        <v>0.2286813263839214</v>
+        <v>0.228753965910616</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2012630369261706</v>
+        <v>0.1992093324677403</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2566666101829358</v>
+        <v>0.2585666101829358</v>
       </c>
       <c r="C100">
-        <v>-44.85522598596208</v>
+        <v>-45.67680739727319</v>
       </c>
       <c r="D100">
-        <v>8.564574014037913</v>
+        <v>8.488092602726798</v>
       </c>
       <c r="E100">
-        <v>66.8098</v>
+        <v>67.5549</v>
       </c>
       <c r="F100">
-        <v>73.01979999999999</v>
+        <v>73.7649</v>
       </c>
       <c r="G100">
         <v>19.6</v>
@@ -9487,37 +9487,37 @@
         <v>3.43</v>
       </c>
       <c r="M100">
-        <v>17.21806884</v>
+        <v>17.39376342</v>
       </c>
       <c r="N100">
-        <v>-13.78806884</v>
+        <v>-13.96376342</v>
       </c>
       <c r="O100">
-        <v>-2.068210326</v>
+        <v>-2.094564513</v>
       </c>
       <c r="P100">
-        <v>-11.719858514</v>
+        <v>-11.869198907</v>
       </c>
       <c r="Q100">
-        <v>-9.209858513999999</v>
+        <v>-9.359198907</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.624386179526603</v>
+        <v>3.202972359053207</v>
       </c>
       <c r="T100">
-        <v>29.94519650193783</v>
+        <v>59.89039300387567</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02988139987016105</v>
+        <v>0.02957956754824023</v>
       </c>
       <c r="W100">
-        <v>0.228753965910616</v>
+        <v>0.228825137972125</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1992093324677403</v>
+        <v>0.1971971169882681</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2585666101829358</v>
-      </c>
-      <c r="C101">
-        <v>-45.67680739727319</v>
-      </c>
-      <c r="D101">
-        <v>8.488092602726798</v>
-      </c>
-      <c r="E101">
-        <v>67.5549</v>
-      </c>
-      <c r="F101">
-        <v>73.7649</v>
-      </c>
-      <c r="G101">
-        <v>19.6</v>
-      </c>
-      <c r="H101">
-        <v>68.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.94</v>
-      </c>
-      <c r="K101">
-        <v>2.51</v>
-      </c>
-      <c r="L101">
-        <v>3.43</v>
-      </c>
-      <c r="M101">
-        <v>17.39376342</v>
-      </c>
-      <c r="N101">
-        <v>-13.96376342</v>
-      </c>
-      <c r="O101">
-        <v>-2.094564513</v>
-      </c>
-      <c r="P101">
-        <v>-11.869198907</v>
-      </c>
-      <c r="Q101">
-        <v>-9.359198907</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.202972359053207</v>
-      </c>
-      <c r="T101">
-        <v>59.89039300387567</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02957956754824023</v>
-      </c>
-      <c r="W101">
-        <v>0.228825137972125</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1971971169882681</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
